--- a/docs/devis/OneWay_Devis_Transport.xlsx
+++ b/docs/devis/OneWay_Devis_Transport.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7785" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Devis Client" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,19 +12,19 @@
     <sheet name="📊 Historique Devis" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'📋 Devis Client'!$A$1:$J$87</definedName>
+    <definedName name="Vehicules">'⚙️ Paramètres'!$B$23:$B$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'📋 Devis Client'!$A$2:$J$72</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot; Ar&quot;"/>
-    <numFmt numFmtId="166" formatCode="0&quot; L/100&quot;"/>
-    <numFmt numFmtId="167" formatCode="&quot;+ &quot;0%"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0&quot; Ar&quot;"/>
+    <numFmt numFmtId="165" formatCode="0&quot; L/100&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;+ &quot;0%"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -38,161 +37,161 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E3A5F"/>
+      <color rgb="FF1E3A5F"/>
       <sz val="22"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00E07B20"/>
+      <color rgb="FFE07B20"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="005B6B7F"/>
+      <color rgb="FF5B6B7F"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E3A5F"/>
+      <color rgb="FF1E3A5F"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF1F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF1F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="005B6B7F"/>
+      <color rgb="FF5B6B7F"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF1F2937"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="005B6B7F"/>
+      <color rgb="FF5B6B7F"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF1F2937"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E3A5F"/>
+      <color rgb="FF1E3A5F"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E3A5F"/>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="005B6B7F"/>
+      <color rgb="FF5B6B7F"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00C0392B"/>
+      <color rgb="FFC0392B"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="005B6B7F"/>
+      <color rgb="FF5B6B7F"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E07B20"/>
+      <color rgb="FFE07B20"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E07B20"/>
+      <color rgb="FFE07B20"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E07B20"/>
+      <color rgb="FFE07B20"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="005B6B7F"/>
+      <color rgb="FF5B6B7F"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF1F2937"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -205,46 +204,46 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E07B20"/>
+        <fgColor rgb="FFE07B20"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002A4A72"/>
+        <fgColor rgb="FF2A4A72"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A5F"/>
+        <fgColor rgb="FF1E3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF0F7"/>
+        <fgColor rgb="FFEAF0F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FC"/>
+        <fgColor rgb="FFF7F9FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F7FB"/>
+        <fgColor rgb="FFF4F7FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C86A10"/>
+        <fgColor rgb="FFC86A10"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -254,23 +253,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </left>
       <right style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </right>
       <top style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9D4E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D4E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D4E0"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D4E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9D4E0"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -278,10 +302,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </right>
       <top style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -289,24 +313,29 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </right>
-      <top style="thin">
-        <color rgb="00C9D4E0"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="FFC9D4E0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
-      <top style="thin">
-        <color rgb="00C9D4E0"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="00C9D4E0"/>
+        <color rgb="FFC9D4E0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -314,14 +343,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -329,304 +352,345 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -705,24 +769,31 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>0</colOff>
+      <colOff>66674</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1428750" cy="1428750"/>
+    <ext cx="1914525" cy="1724024"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
-      <blipFill>
+      <blipFill rotWithShape="1">
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="12556" t="7071" r="9866" b="13131"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:xfrm>
+          <a:off x="266699" y="0"/>
+          <a:ext cx="1914525" cy="1724024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1019,1718 +1090,1253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001E3A5F"/>
+    <tabColor rgb="FF1E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:J73"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="0.5703125" customWidth="1" style="74" min="1" max="1"/>
+    <col width="30" customWidth="1" style="74" min="2" max="2"/>
+    <col width="20" customWidth="1" style="74" min="3" max="3"/>
+    <col width="25.5703125" customWidth="1" style="74" min="4" max="4"/>
+    <col width="15.28515625" customWidth="1" style="74" min="5" max="5"/>
+    <col width="19.7109375" customWidth="1" style="74" min="6" max="6"/>
+    <col width="16" customWidth="1" style="74" min="7" max="8"/>
+    <col width="14" customWidth="1" style="74" min="9" max="9"/>
+    <col width="3" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="18" customHeight="1"/>
-    <row r="3" ht="18" customHeight="1">
-      <c r="E3" s="1" t="inlineStr">
+    <row r="1" ht="8.25" customHeight="1" s="74">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="74"/>
+    <row r="4" ht="18" customHeight="1" s="74">
+      <c r="E4" s="89" t="inlineStr">
         <is>
           <t>DEVIS DE TRANSPORT</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1"/>
-    <row r="5" ht="18" customHeight="1">
-      <c r="E5" s="2" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="74"/>
+    <row r="6" ht="18" customHeight="1" s="74">
+      <c r="E6" s="90" t="inlineStr">
         <is>
           <t>Transport · Livraison · Suivi Digital</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1"/>
-    <row r="7" ht="18" customHeight="1"/>
-    <row r="8" ht="18" customHeight="1"/>
-    <row r="9" ht="4" customHeight="1">
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="74"/>
+    <row r="8" ht="18" customHeight="1" s="74"/>
+    <row r="9" ht="18" customHeight="1" s="74"/>
+    <row r="10" ht="8.25" customHeight="1" s="74">
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+      <c r="H10" s="1" t="n"/>
+      <c r="I10" s="1" t="n"/>
+    </row>
+    <row r="11" ht="6" customHeight="1" s="74"/>
+    <row r="12" ht="20.1" customHeight="1" s="74">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>N° DEVIS :</t>
         </is>
       </c>
-      <c r="C11" s="5">
+      <c r="C12" s="108">
         <f>"OW-"&amp;TEXT('⚙️ Paramètres'!C9,"0000")&amp;"-"&amp;TEXT(TODAY(),"MMYYYY")</f>
         <v/>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>DATE :</t>
         </is>
       </c>
-      <c r="F11" s="6">
+      <c r="F12" s="4">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>VALIDE JUSQU'AU :</t>
         </is>
       </c>
-      <c r="H11" s="8">
+      <c r="H12" s="6">
         <f>TODAY()+'⚙️ Paramètres'!C13</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="6" customHeight="1"/>
-    <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="9" t="inlineStr">
+    <row r="13" ht="6" customHeight="1" s="74"/>
+    <row r="14" ht="20.1" customHeight="1" s="74">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">  👤  INFORMATIONS CLIENT</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F14" s="82" t="inlineStr">
         <is>
           <t xml:space="preserve">  🚛  ONE WAY — TRANSPORT</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="74">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Nom / Société :</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="73" t="inlineStr">
         <is>
           <t>Nom du client</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Société :</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G15" s="73" t="inlineStr">
         <is>
           <t>One Way SARL</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="18" customHeight="1" s="74">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C16" s="73" t="inlineStr">
         <is>
           <t>Adresse complète</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G16" s="73" t="inlineStr">
         <is>
           <t>Antananarivo, Madagascar</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17" ht="18" customHeight="1" s="74">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Ville :</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="73" t="inlineStr">
         <is>
           <t>Antananarivo</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Téléphone :</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G17" s="73" t="inlineStr">
         <is>
           <t>+261 XX XXX XX XX</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="18" customHeight="1" s="74">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Téléphone :</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C18" s="73" t="inlineStr">
         <is>
           <t>+261 XX XXX XX XX</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Email :</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G18" s="73" t="inlineStr">
         <is>
           <t>contact@oneway.mg</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19" ht="18" customHeight="1" s="74">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Email :</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C19" s="73" t="inlineStr">
         <is>
           <t>client@email.mg</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>MVola :</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G19" s="73" t="inlineStr">
         <is>
           <t>0XX XX XXX XX</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="18" customHeight="1" s="74">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>N° Client :</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="73" t="inlineStr">
         <is>
           <t>OW-CLI-001</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>NIF / STAT :</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G20" s="73" t="inlineStr">
         <is>
           <t>XXX XXX XXX</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="6" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="12" t="inlineStr">
+    <row r="21" ht="6" customHeight="1" s="74"/>
+    <row r="22" ht="21.95" customHeight="1" s="74">
+      <c r="B22" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  📍  PARAMÈTRES DU TRANSPORT</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="23" ht="18" customHeight="1" s="74">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Point de chargement :</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C23" s="73" t="inlineStr">
         <is>
           <t>Antananarivo</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Point de livraison :</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G23" s="73" t="inlineStr">
         <is>
           <t>Toamasina</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="18" customHeight="1" s="74">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Distance estimée (km) :</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C24" s="73" t="n">
         <v>357</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Trajet :</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G24" s="73" t="inlineStr">
         <is>
           <t>Aller-retour</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+    <row r="25" ht="18" customHeight="1" s="74">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Type de véhicule :</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Camion 5 tonnes</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="C25" s="73" t="inlineStr">
+        <is>
+          <t>🚚 Camion 5 tonnes</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Type de marchandise :</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G25" s="73" t="inlineStr">
         <is>
           <t>Générale</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="18" customHeight="1" s="74">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Date de transport :</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C26" s="73" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Durée estimée :</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G26" s="73" t="inlineStr">
         <is>
           <t>5h30 (aller)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
+    <row r="27" ht="18" customHeight="1" s="74">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Type de route :</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C27" s="73" t="inlineStr">
         <is>
           <t>Route nationale</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Conditions particulières :</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G27" s="73" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
+    <row r="28" ht="6" customHeight="1" s="74"/>
+    <row r="29" ht="21.95" customHeight="1" s="74">
+      <c r="B29" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  📦  DÉTAIL DES PRESTATIONS</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="B29" s="13" t="inlineStr">
+    <row r="30" ht="24" customHeight="1" s="74">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C30" s="88" t="inlineStr">
         <is>
           <t>DÉSIGNATION / DESCRIPTION</t>
         </is>
       </c>
-      <c r="D29" s="109" t="n"/>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="D30" s="72" t="n"/>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>QTÉ</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>UNITÉ</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>P.U. (Ar)</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>TOTAL (Ar)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="B30" s="16" t="n">
+    <row r="31" ht="18.95" customHeight="1" s="74">
+      <c r="B31" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C31" s="71" t="inlineStr">
         <is>
           <t>Transport marchandises — aller (chargé), tarif km</t>
         </is>
       </c>
-      <c r="D30" s="109" t="n"/>
-      <c r="E30" s="19" t="inlineStr">
+      <c r="D31" s="72" t="n"/>
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="F30" s="20" t="n">
-        <v>357</v>
-      </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="F31" s="11">
+        <f>$C$24</f>
+        <v/>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>km</t>
         </is>
       </c>
-      <c r="H30" s="21" t="n">
-        <v>2800</v>
-      </c>
-      <c r="I30" s="22">
-        <f>F30*H30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="B31" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>Carburant aller (gasoil) — selon véhicule</t>
-        </is>
-      </c>
-      <c r="D31" s="109" t="n"/>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="H31" s="12">
+        <f>INDEX('⚙️ Paramètres'!$D$23:$D$32,MATCH($C$25,'⚙️ Paramètres'!$B$23:$B$32,0))</f>
+        <v/>
+      </c>
+      <c r="I31" s="13">
+        <f>F31*H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="18.95" customHeight="1" s="74">
+      <c r="B32" s="14">
+        <f>B31+1</f>
+        <v/>
+      </c>
+      <c r="C32" s="86" t="inlineStr">
+        <is>
+          <t>Carburant aller-retour (selon véhicule)</t>
+        </is>
+      </c>
+      <c r="D32" s="72" t="n"/>
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Carburant</t>
         </is>
       </c>
-      <c r="F31" s="27" t="n">
-        <v>89</v>
-      </c>
-      <c r="G31" s="26" t="inlineStr">
+      <c r="F32" s="17">
+        <f>ROUND($C$24*2*INDEX('⚙️ Paramètres'!$E$23:$E$32,MATCH($C$25,'⚙️ Paramètres'!$B$23:$B$32,0))/100,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>litre</t>
         </is>
       </c>
-      <c r="H31" s="28">
-        <f>'⚙️ Paramètres'!C18</f>
-        <v/>
-      </c>
-      <c r="I31" s="29">
-        <f>F31*H31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="B32" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>Retour véhicule à vide (repositionnement)</t>
-        </is>
-      </c>
-      <c r="D32" s="109" t="n"/>
-      <c r="E32" s="26" t="inlineStr">
-        <is>
-          <t>Aller-retour</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n">
+      <c r="H32" s="18">
+        <f>ROUND(INDEX('⚙️ Paramètres'!$F$23:$F$32,MATCH($C$25,'⚙️ Paramètres'!$B$23:$B$32,0))*100/INDEX('⚙️ Paramètres'!$E$23:$E$32,MATCH($C$25,'⚙️ Paramètres'!$B$23:$B$32,0)),0)</f>
+        <v/>
+      </c>
+      <c r="I32" s="19">
+        <f>F32*H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18.95" customHeight="1" s="74">
+      <c r="B33" s="14">
+        <f>B32+1</f>
+        <v/>
+      </c>
+      <c r="C33" s="76" t="inlineStr">
+        <is>
+          <t>Forfait prise en charge / frais fixes de base</t>
+        </is>
+      </c>
+      <c r="D33" s="72" t="n"/>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="26" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H32" s="28">
-        <f>ROUND((I30+I31)*'⚙️ Paramètres'!C15,0)</f>
-        <v/>
-      </c>
-      <c r="I32" s="29">
-        <f>F32*H32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="B33" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>Forfait prise en charge / frais fixes de base</t>
-        </is>
-      </c>
-      <c r="D33" s="109" t="n"/>
-      <c r="E33" s="33" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="F33" s="34" t="n">
+      <c r="H33" s="24" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I33" s="25">
+        <f>F34*H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="18.95" customHeight="1" s="74">
+      <c r="B34" s="14">
+        <f>B33+1</f>
+        <v/>
+      </c>
+      <c r="C34" s="71" t="inlineStr">
+        <is>
+          <t>Majoration type de marchandise (coefficient)</t>
+        </is>
+      </c>
+      <c r="D34" s="72" t="n"/>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Supplément</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="13">
+        <f>F35*H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="18.95" customHeight="1" s="74">
+      <c r="B35" s="14">
+        <f>B34+1</f>
+        <v/>
+      </c>
+      <c r="C35" s="76" t="inlineStr">
+        <is>
+          <t>Manutention au chargement</t>
+        </is>
+      </c>
+      <c r="D35" s="72" t="n"/>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>Main d'œuvre</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="33" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H33" s="35" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I33" s="36">
-        <f>F33*H33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="B34" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>Majoration type de marchandise (coefficient)</t>
-        </is>
-      </c>
-      <c r="D34" s="109" t="n"/>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="H35" s="24" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I35" s="25">
+        <f>F36*H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18.95" customHeight="1" s="74">
+      <c r="B36" s="14">
+        <f>B35+1</f>
+        <v/>
+      </c>
+      <c r="C36" s="71" t="inlineStr">
+        <is>
+          <t>Manutention au déchargement</t>
+        </is>
+      </c>
+      <c r="D36" s="72" t="n"/>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Main d'œuvre</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I36" s="13">
+        <f>F37*H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="18.95" customHeight="1" s="74">
+      <c r="B37" s="14">
+        <f>B36+1</f>
+        <v/>
+      </c>
+      <c r="C37" s="76" t="inlineStr">
+        <is>
+          <t>Arrimage / sanglage / bâchage</t>
+        </is>
+      </c>
+      <c r="D37" s="72" t="n"/>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>Sécurité</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I37" s="25">
+        <f>F38*H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="18.95" customHeight="1" s="74">
+      <c r="B38" s="14">
+        <f>B37+1</f>
+        <v/>
+      </c>
+      <c r="C38" s="76" t="inlineStr">
+        <is>
+          <t>Assurance marchandise (% valeur déclarée)</t>
+        </is>
+      </c>
+      <c r="D38" s="72" t="n"/>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>Assurance</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>% valeur</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="25">
+        <f>F39*H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18.95" customHeight="1" s="74">
+      <c r="B39" s="14">
+        <f>B38+1</f>
+        <v/>
+      </c>
+      <c r="C39" s="76" t="inlineStr">
+        <is>
+          <t>Gardiennage / stationnement de nuit</t>
+        </is>
+      </c>
+      <c r="D39" s="72" t="n"/>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>Sécurité</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>nuit</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I39" s="25">
+        <f>F40*H40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18.95" customHeight="1" s="74">
+      <c r="B40" s="14">
+        <f>B39+1</f>
+        <v/>
+      </c>
+      <c r="C40" s="76" t="inlineStr">
+        <is>
+          <t>Supplément frigorifique (groupe froid / jour)</t>
+        </is>
+      </c>
+      <c r="D40" s="72" t="n"/>
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>Supplément</t>
         </is>
       </c>
-      <c r="F34" s="20" t="n">
+      <c r="F40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>jour</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I40" s="25">
+        <f>F41*H41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="18.95" customHeight="1" s="74">
+      <c r="B41" s="14">
+        <f>B40+1</f>
+        <v/>
+      </c>
+      <c r="C41" s="71" t="inlineStr">
+        <is>
+          <t>Frais administratifs / documentation</t>
+        </is>
+      </c>
+      <c r="D41" s="72" t="n"/>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Administratif</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I41" s="13">
+        <f>F42*H42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18.95" customHeight="1" s="74">
+      <c r="B42" s="14">
+        <f>B41+1</f>
+        <v/>
+      </c>
+      <c r="C42" s="71" t="inlineStr">
+        <is>
+          <t>Ristournes / frais de barrière communale</t>
+        </is>
+      </c>
+      <c r="D42" s="72" t="n"/>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Administratif</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H34" s="21" t="n">
+      <c r="H42" s="12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I42" s="13">
+        <f>F43*H43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" s="74">
+      <c r="B43" s="14">
+        <f>B42+1</f>
+        <v/>
+      </c>
+      <c r="C43" s="76" t="inlineStr">
+        <is>
+          <t>Emballage / palettisation / film étirable</t>
+        </is>
+      </c>
+      <c r="D43" s="72" t="n"/>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>Conditionnement</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="22">
-        <f>F34*H34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="B35" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <t>Manutention au chargement</t>
-        </is>
-      </c>
-      <c r="D35" s="109" t="n"/>
-      <c r="E35" s="33" t="inlineStr">
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I43" s="25">
+        <f>F44*H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="74">
+      <c r="B44" s="14">
+        <f>B43+1</f>
+        <v/>
+      </c>
+      <c r="C44" s="71" t="inlineStr">
+        <is>
+          <t>Stockage / entreposage temporaire</t>
+        </is>
+      </c>
+      <c r="D44" s="72" t="n"/>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>jour</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I44" s="13">
+        <f>F45*H45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="18.95" customHeight="1" s="74">
+      <c r="B45" s="14">
+        <f>B44+1</f>
+        <v/>
+      </c>
+      <c r="C45" s="76" t="inlineStr">
+        <is>
+          <t>Chauffeur supplémentaire (longue distance)</t>
+        </is>
+      </c>
+      <c r="D45" s="72" t="n"/>
+      <c r="E45" s="22" t="inlineStr">
         <is>
           <t>Main d'œuvre</t>
         </is>
       </c>
-      <c r="F35" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="33" t="inlineStr">
+      <c r="F45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>jour</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I45" s="25">
+        <f>F46*H46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="18.95" customHeight="1" s="74">
+      <c r="B46" s="14">
+        <f>B45+1</f>
+        <v/>
+      </c>
+      <c r="C46" s="76" t="inlineStr">
+        <is>
+          <t>Nettoyage / désinfection caisse (denrées, animaux)</t>
+        </is>
+      </c>
+      <c r="D46" s="72" t="n"/>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>Entretien</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="22" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H35" s="35" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I35" s="36">
-        <f>F35*H35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="B36" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>Manutention au déchargement</t>
-        </is>
-      </c>
-      <c r="D36" s="109" t="n"/>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>Main d'œuvre</t>
-        </is>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="H46" s="24" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I46" s="25">
+        <f>F47*H47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="18.95" customHeight="1" s="74">
+      <c r="B47" s="14">
+        <f>B46+1</f>
+        <v/>
+      </c>
+      <c r="C47" s="71" t="inlineStr">
+        <is>
+          <t>Supplément saison des pluies / piste dégradée</t>
+        </is>
+      </c>
+      <c r="D47" s="72" t="n"/>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Supplément</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="H36" s="21" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I36" s="22">
-        <f>F36*H36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="B37" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>Arrimage / sanglage / bâchage</t>
-        </is>
-      </c>
-      <c r="D37" s="109" t="n"/>
-      <c r="E37" s="33" t="inlineStr">
-        <is>
-          <t>Sécurité</t>
-        </is>
-      </c>
-      <c r="F37" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="33" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H37" s="35" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I37" s="36">
-        <f>F37*H37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="B38" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>Suivi GPS temps réel (plateforme ONE WAY)</t>
-        </is>
-      </c>
-      <c r="D38" s="109" t="n"/>
-      <c r="E38" s="26" t="inlineStr">
-        <is>
-          <t>Digital</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="26" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H38" s="28" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I38" s="29">
-        <f>F38*H38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="B39" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="C39" s="31" t="inlineStr">
-        <is>
-          <t>Assurance marchandise (% valeur déclarée)</t>
-        </is>
-      </c>
-      <c r="D39" s="109" t="n"/>
-      <c r="E39" s="33" t="inlineStr">
-        <is>
-          <t>Assurance</t>
-        </is>
-      </c>
-      <c r="F39" s="34" t="n">
+      <c r="H47" s="12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I47" s="13">
+        <f>F48*H48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20.1" customHeight="1" s="74">
+      <c r="B48" s="116" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL H.T.</t>
+        </is>
+      </c>
+      <c r="C48" s="117" t="n"/>
+      <c r="D48" s="117" t="n"/>
+      <c r="E48" s="117" t="n"/>
+      <c r="F48" s="118" t="n"/>
+      <c r="G48" s="119">
+        <f>SUM(I31:I47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="117" t="n"/>
+      <c r="I48" s="118" t="n"/>
+    </row>
+    <row r="49" ht="20.1" customHeight="1" s="74">
+      <c r="B49" s="83" t="inlineStr">
+        <is>
+          <t>Remise commerciale (%)  →</t>
+        </is>
+      </c>
+      <c r="F49" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="33" t="inlineStr">
-        <is>
-          <t>% valeur</t>
-        </is>
-      </c>
-      <c r="H39" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="36">
-        <f>F39*H39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="B40" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>Accompagnement douane / portuaire</t>
-        </is>
-      </c>
-      <c r="D40" s="109" t="n"/>
-      <c r="E40" s="19" t="inlineStr">
-        <is>
-          <t>Administratif</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="19" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H40" s="21" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I40" s="22">
-        <f>F40*H40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="B41" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>Gardiennage / stationnement de nuit</t>
-        </is>
-      </c>
-      <c r="D41" s="109" t="n"/>
-      <c r="E41" s="33" t="inlineStr">
-        <is>
-          <t>Sécurité</t>
-        </is>
-      </c>
-      <c r="F41" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="33" t="inlineStr">
-        <is>
-          <t>nuit</t>
-        </is>
-      </c>
-      <c r="H41" s="35" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I41" s="36">
-        <f>F41*H41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="B42" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>Heure(s) d'attente (&gt;2h offert)</t>
-        </is>
-      </c>
-      <c r="D42" s="109" t="n"/>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>Attente</t>
-        </is>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="19" t="inlineStr">
-        <is>
-          <t>heure</t>
-        </is>
-      </c>
-      <c r="H42" s="21" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I42" s="22">
-        <f>F42*H42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="B43" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="C43" s="31" t="inlineStr">
-        <is>
-          <t>Supplément frigorifique (groupe froid / jour)</t>
-        </is>
-      </c>
-      <c r="D43" s="109" t="n"/>
-      <c r="E43" s="33" t="inlineStr">
-        <is>
-          <t>Supplément</t>
-        </is>
-      </c>
-      <c r="F43" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="33" t="inlineStr">
-        <is>
-          <t>jour</t>
-        </is>
-      </c>
-      <c r="H43" s="35" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I43" s="36">
-        <f>F43*H43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="B44" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>Escorte / convoi exceptionnel</t>
-        </is>
-      </c>
-      <c r="D44" s="109" t="n"/>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>Supplément</t>
-        </is>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="19" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H44" s="21" t="n">
-        <v>120000</v>
-      </c>
-      <c r="I44" s="22">
-        <f>F44*H44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="B45" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>Service express (J+1, majoré)</t>
-        </is>
-      </c>
-      <c r="D45" s="109" t="n"/>
-      <c r="E45" s="33" t="inlineStr">
-        <is>
-          <t>Supplément</t>
-        </is>
-      </c>
-      <c r="F45" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="33" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="36">
-        <f>F45*H45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="B46" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>Frais administratifs / documentation</t>
-        </is>
-      </c>
-      <c r="D46" s="109" t="n"/>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>Administratif</t>
-        </is>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="19" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H46" s="21" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I46" s="22">
-        <f>F46*H46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="B47" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="C47" s="31" t="inlineStr">
-        <is>
-          <t>Frais de bac / traversée fluviale</t>
-        </is>
-      </c>
-      <c r="D47" s="109" t="n"/>
-      <c r="E47" s="33" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="F47" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="33" t="inlineStr">
-        <is>
-          <t>traversée</t>
-        </is>
-      </c>
-      <c r="H47" s="35" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I47" s="36">
-        <f>F47*H47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="B48" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>Ristournes / frais de barrière communale</t>
-        </is>
-      </c>
-      <c r="D48" s="109" t="n"/>
-      <c r="E48" s="19" t="inlineStr">
-        <is>
-          <t>Administratif</t>
-        </is>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="19" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H48" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I48" s="22">
-        <f>F48*H48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="B49" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="C49" s="31" t="inlineStr">
-        <is>
-          <t>Emballage / palettisation / film étirable</t>
-        </is>
-      </c>
-      <c r="D49" s="109" t="n"/>
-      <c r="E49" s="33" t="inlineStr">
-        <is>
-          <t>Conditionnement</t>
-        </is>
-      </c>
-      <c r="F49" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="33" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H49" s="35" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I49" s="36">
-        <f>F49*H49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="B50" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>Hayon élévateur / transpalette (livraison)</t>
-        </is>
-      </c>
-      <c r="D50" s="109" t="n"/>
-      <c r="E50" s="19" t="inlineStr">
-        <is>
-          <t>Manutention</t>
-        </is>
-      </c>
-      <c r="F50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="19" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H50" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I50" s="22">
-        <f>F50*H50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="B51" s="30" t="n">
-        <v>22</v>
-      </c>
-      <c r="C51" s="31" t="inlineStr">
-        <is>
-          <t>Livraison à l'étage / portage manuel</t>
-        </is>
-      </c>
-      <c r="D51" s="109" t="n"/>
-      <c r="E51" s="33" t="inlineStr">
-        <is>
-          <t>Main d'œuvre</t>
-        </is>
-      </c>
-      <c r="F51" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="33" t="inlineStr">
-        <is>
-          <t>étage</t>
-        </is>
-      </c>
-      <c r="H51" s="35" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I51" s="36">
-        <f>F51*H51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="B52" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>Stockage / entreposage temporaire</t>
-        </is>
-      </c>
-      <c r="D52" s="109" t="n"/>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>Logistique</t>
-        </is>
-      </c>
-      <c r="F52" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>jour</t>
-        </is>
-      </c>
-      <c r="H52" s="21" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I52" s="22">
-        <f>F52*H52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="B53" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="C53" s="31" t="inlineStr">
-        <is>
-          <t>Chauffeur supplémentaire (longue distance)</t>
-        </is>
-      </c>
-      <c r="D53" s="109" t="n"/>
-      <c r="E53" s="33" t="inlineStr">
-        <is>
-          <t>Main d'œuvre</t>
-        </is>
-      </c>
-      <c r="F53" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="33" t="inlineStr">
-        <is>
-          <t>jour</t>
-        </is>
-      </c>
-      <c r="H53" s="35" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I53" s="36">
-        <f>F53*H53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="B54" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>Frais de mission chauffeur (nuitée + repas)</t>
-        </is>
-      </c>
-      <c r="D54" s="109" t="n"/>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>Frais</t>
-        </is>
-      </c>
-      <c r="F54" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="19" t="inlineStr">
-        <is>
-          <t>nuitée</t>
-        </is>
-      </c>
-      <c r="H54" s="21" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I54" s="22">
-        <f>F54*H54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="B55" s="30" t="n">
-        <v>26</v>
-      </c>
-      <c r="C55" s="31" t="inlineStr">
-        <is>
-          <t>Point de chargement / livraison supplémentaire</t>
-        </is>
-      </c>
-      <c r="D55" s="109" t="n"/>
-      <c r="E55" s="33" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="F55" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="33" t="inlineStr">
-        <is>
-          <t>point</t>
-        </is>
-      </c>
-      <c r="H55" s="35" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I55" s="36">
-        <f>F55*H55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="B56" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>Relivraison (destinataire absent)</t>
-        </is>
-      </c>
-      <c r="D56" s="109" t="n"/>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="19" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H56" s="21" t="n">
-        <v>35000</v>
-      </c>
-      <c r="I56" s="22">
-        <f>F56*H56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="B57" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="C57" s="24" t="inlineStr">
-        <is>
-          <t>Preuve de livraison numérique (photos + e-signature)</t>
-        </is>
-      </c>
-      <c r="D57" s="109" t="n"/>
-      <c r="E57" s="26" t="inlineStr">
-        <is>
-          <t>Digital</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="26" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H57" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="29">
-        <f>F57*H57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="B58" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>Encaissement à la livraison (Mobile Money / COD)</t>
-        </is>
-      </c>
-      <c r="D58" s="109" t="n"/>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>Financier</t>
-        </is>
-      </c>
-      <c r="F58" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="19" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H58" s="21" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I58" s="22">
-        <f>F58*H58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="B59" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="C59" s="31" t="inlineStr">
-        <is>
-          <t>Surestaries / immobilisation conteneur</t>
-        </is>
-      </c>
-      <c r="D59" s="109" t="n"/>
-      <c r="E59" s="33" t="inlineStr">
-        <is>
-          <t>Supplément</t>
-        </is>
-      </c>
-      <c r="F59" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="33" t="inlineStr">
-        <is>
-          <t>jour</t>
-        </is>
-      </c>
-      <c r="H59" s="35" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I59" s="36">
-        <f>F59*H59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="B60" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>Empotage / dépotage conteneur</t>
-        </is>
-      </c>
-      <c r="D60" s="109" t="n"/>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>Main d'œuvre</t>
-        </is>
-      </c>
-      <c r="F60" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="19" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H60" s="21" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I60" s="22">
-        <f>F60*H60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="B61" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="C61" s="31" t="inlineStr">
-        <is>
-          <t>Nettoyage / désinfection caisse (denrées, animaux)</t>
-        </is>
-      </c>
-      <c r="D61" s="109" t="n"/>
-      <c r="E61" s="33" t="inlineStr">
-        <is>
-          <t>Entretien</t>
-        </is>
-      </c>
-      <c r="F61" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="33" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H61" s="35" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I61" s="36">
-        <f>F61*H61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="B62" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>Supplément saison des pluies / piste dégradée</t>
-        </is>
-      </c>
-      <c r="D62" s="109" t="n"/>
-      <c r="E62" s="19" t="inlineStr">
-        <is>
-          <t>Supplément</t>
-        </is>
-      </c>
-      <c r="F62" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="19" t="inlineStr">
-        <is>
-          <t>forfait</t>
-        </is>
-      </c>
-      <c r="H62" s="21" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I62" s="22">
-        <f>F62*H62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="B63" s="37" t="inlineStr">
-        <is>
-          <t>SOUS-TOTAL H.T.</t>
-        </is>
-      </c>
-      <c r="G63" s="39">
-        <f>SUM(I30:I62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="B64" s="40" t="inlineStr">
-        <is>
-          <t>Remise commerciale (%)  →</t>
-        </is>
-      </c>
-      <c r="F64" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="42">
-        <f>-ROUND(G63*F64/100,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="B65" s="37" t="inlineStr">
+      <c r="G49" s="84">
+        <f>-ROUND(G48*F49/100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20.1" customHeight="1" s="74">
+      <c r="B50" s="91" t="inlineStr">
         <is>
           <t>Base imposable (après remise)</t>
         </is>
       </c>
-      <c r="G65" s="39">
-        <f>G63+G64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="B66" s="40" t="inlineStr">
+      <c r="G50" s="75">
+        <f>G48+G49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20.1" customHeight="1" s="74">
+      <c r="B51" s="83" t="inlineStr">
         <is>
           <t>TVA (Oui / Non)  →</t>
         </is>
       </c>
-      <c r="F66" s="43" t="inlineStr">
+      <c r="F51" s="27" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="G66" s="44">
-        <f>IF(F66="Oui",ROUND(G65*0.2,0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="B67" s="45" t="inlineStr">
+      <c r="G51" s="87">
+        <f>IF(F51="Oui",ROUND(G50*0.2,0),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1" s="74">
+      <c r="B52" s="92" t="inlineStr">
         <is>
           <t>💰  TOTAL À PAYER (TTC)</t>
         </is>
       </c>
-      <c r="G67" s="47">
-        <f>G65+G66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69" ht="22" customHeight="1">
-      <c r="B69" s="12" t="inlineStr">
+      <c r="G52" s="93">
+        <f>G50+G51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" s="74">
+      <c r="B53" s="92" t="n"/>
+      <c r="G53" s="93" t="n"/>
+    </row>
+    <row r="54" ht="21.95" customHeight="1" s="74">
+      <c r="B54" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  💳  CONDITIONS DE PAIEMENT</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="4" t="inlineStr">
+    <row r="55" ht="18" customHeight="1" s="74">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Mode de paiement :</t>
         </is>
       </c>
-      <c r="C70" s="48" t="inlineStr">
+      <c r="C55" s="81" t="inlineStr">
         <is>
           <t>MVola / Orange Money / Airtel Money / Virement / Espèces</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="B71" s="4" t="inlineStr">
+    <row r="56" ht="18" customHeight="1" s="74">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Acompte requis :</t>
         </is>
       </c>
-      <c r="C71" s="48" t="inlineStr">
+      <c r="C56" s="81" t="inlineStr">
         <is>
           <t>50% à la commande — 50% à la livraison</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="4" t="inlineStr">
+    <row r="57" ht="18" customHeight="1" s="74">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>N° MVola One Way :</t>
         </is>
       </c>
-      <c r="C72" s="48" t="inlineStr">
+      <c r="C57" s="81" t="inlineStr">
         <is>
           <t>0XX XX XXX XX</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="4" t="inlineStr">
+    <row r="58" ht="18" customHeight="1" s="74">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Délai de paiement :</t>
         </is>
       </c>
-      <c r="C73" s="48" t="inlineStr">
+      <c r="C58" s="81" t="inlineStr">
         <is>
           <t>Paiement à réception ou selon accord</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="B74" s="4" t="inlineStr">
+    <row r="59" ht="18" customHeight="1" s="74">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Pénalités de retard :</t>
         </is>
       </c>
-      <c r="C74" s="48" t="inlineStr">
+      <c r="C59" s="81" t="inlineStr">
         <is>
           <t>2% par semaine de retard</t>
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76" ht="22" customHeight="1">
-      <c r="B76" s="12" t="inlineStr">
+    <row r="60" s="74">
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="81" t="n"/>
+    </row>
+    <row r="61" ht="21.95" customHeight="1" s="74">
+      <c r="B61" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  📝  CONDITIONS GÉNÉRALES</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="B77" s="49" t="inlineStr">
+    <row r="62" ht="15.95" customHeight="1" s="74">
+      <c r="B62" s="78" t="inlineStr">
         <is>
           <t>• Ce devis est valable 30 jours à compter de la date d'émission.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="B78" s="49" t="inlineStr">
+    <row r="63" ht="15.95" customHeight="1" s="74">
+      <c r="B63" s="78" t="inlineStr">
         <is>
           <t>• Prix en Ariary (MGA) HT sauf mention contraire. Trajet facturé ALLER-RETOUR (le véhicule revient à son point de départ).</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="B79" s="49" t="inlineStr">
+    <row r="64" ht="15.95" customHeight="1" s="74">
+      <c r="B64" s="78" t="inlineStr">
         <is>
           <t>• Le carburant est facturé au prix réel de la pompe ; un avenant s'applique en cas de forte variation du cours du gasoil.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="B80" s="49" t="inlineStr">
+    <row r="65" ht="15.95" customHeight="1" s="74">
+      <c r="B65" s="78" t="inlineStr">
         <is>
           <t>• Force majeure (météo, route coupée) : avenant tarifaire applicable.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="B81" s="49" t="inlineStr">
+    <row r="66" ht="15.95" customHeight="1" s="74">
+      <c r="B66" s="78" t="inlineStr">
         <is>
           <t>• Responsabilité limitée à la valeur déclarée des marchandises.</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="B82" s="49" t="inlineStr">
+    <row r="67" ht="15.95" customHeight="1" s="74">
+      <c r="B67" s="78" t="inlineStr">
         <is>
           <t>• Pour toute modification, contactez-nous 48h avant le transport.</t>
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84" ht="50" customHeight="1">
-      <c r="B84" s="50" t="inlineStr">
+    <row r="68" s="74">
+      <c r="B68" s="78" t="n"/>
+    </row>
+    <row r="69" ht="50.1" customHeight="1" s="74">
+      <c r="B69" s="77" t="inlineStr">
         <is>
           <t>Signature &amp; Cachet Client</t>
         </is>
       </c>
-      <c r="F84" s="50" t="inlineStr">
+      <c r="F69" s="77" t="inlineStr">
         <is>
           <t>Pour One Way</t>
         </is>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87" ht="22" customHeight="1">
-      <c r="B87" s="51" t="inlineStr">
+    <row r="70" s="74">
+      <c r="B70" s="77" t="n"/>
+      <c r="F70" s="77" t="n"/>
+    </row>
+    <row r="71"/>
+    <row r="72" ht="21.95" customHeight="1" s="74">
+      <c r="B72" s="85" t="inlineStr">
         <is>
           <t>One Way SARL  ·  Transport · Livraison · Suivi Digital  ·  Antananarivo, Madagascar 🇲🇬</t>
         </is>
       </c>
     </row>
+    <row r="73" s="74"/>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="C62:D62"/>
+  <mergeCells count="72">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E6:I7"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="B51:E51"/>
     <mergeCell ref="G15:I15"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="F14:I14"/>
     <mergeCell ref="G24:I24"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F69:I69"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C17:E17"/>
     <mergeCell ref="G26:I26"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="F84:I84"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B67:I67"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="C58:I58"/>
+    <mergeCell ref="G25:I25"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="G16:I16"/>
-    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B76:I76"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C71:I71"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B78:I78"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="B87:I87"/>
+    <mergeCell ref="G52:I52"/>
     <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="C70:I70"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B77:I77"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C74:I74"/>
-    <mergeCell ref="E3:I4"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E5:I6"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C55:I55"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="E4:I5"/>
+    <mergeCell ref="C56:I56"/>
+    <mergeCell ref="B69:E69"/>
     <mergeCell ref="G23:I23"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B81:I81"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="C72:I72"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C73:I73"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="G67:I67"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="C59:I59"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C25:E25"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Type de véhicule" error="Choisissez un type de véhicule dans la liste." type="list">
+      <formula1>Vehicules</formula1>
+    </dataValidation>
+    <dataValidation sqref="F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2738,26 +2344,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002A4A72"/>
+    <tabColor rgb="FF2A4A72"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:H62"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" style="74" min="1" max="1"/>
+    <col width="30" customWidth="1" style="74" min="2" max="2"/>
+    <col width="16" customWidth="1" style="74" min="3" max="3"/>
+    <col width="17" customWidth="1" style="74" min="4" max="4"/>
+    <col width="14" customWidth="1" style="74" min="5" max="5"/>
+    <col width="16" customWidth="1" style="74" min="6" max="6"/>
+    <col width="15" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="3" customWidth="1" style="74" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="52" t="inlineStr">
+      <c r="B2" s="99" t="inlineStr">
         <is>
           <t>⚙️  PARAMÈTRES &amp; TARIFS DE RÉFÉRENCE — ONE WAY</t>
         </is>
@@ -2766,1202 +2372,1202 @@
     <row r="3"/>
     <row r="4"/>
     <row r="5"/>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+    <row r="6" ht="8.1" customHeight="1" s="74"/>
+    <row r="8" ht="21.95" customHeight="1" s="74">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  🏢  INFORMATIONS GÉNÉRALES</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="53" t="inlineStr">
+    <row r="9" ht="20.1" customHeight="1" s="74">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Numéro séquence devis</t>
         </is>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="55" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="E9" s="56" t="inlineStr">
+      <c r="E9" s="101" t="inlineStr">
         <is>
           <t>Auto-incrémenté</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="53" t="inlineStr">
+    <row r="10" ht="20.1" customHeight="1" s="74">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Remise commerciale défaut</t>
         </is>
       </c>
-      <c r="C10" s="54" t="n">
+      <c r="C10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="55" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E10" s="56" t="inlineStr">
+      <c r="E10" s="101" t="inlineStr">
         <is>
           <t>0 si aucune remise</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="53" t="inlineStr">
+    <row r="11" ht="20.1" customHeight="1" s="74">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>TVA applicable par défaut</t>
         </is>
       </c>
-      <c r="C11" s="54" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="D11" s="55" t="inlineStr"/>
-      <c r="E11" s="56" t="inlineStr">
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="101" t="inlineStr">
         <is>
           <t>Oui ou Non</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="53" t="inlineStr">
+    <row r="12" ht="20.1" customHeight="1" s="74">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Devise</t>
         </is>
       </c>
-      <c r="C12" s="54" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Ariary (MGA)</t>
         </is>
       </c>
-      <c r="D12" s="55" t="inlineStr"/>
-      <c r="E12" s="56" t="inlineStr">
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="101" t="inlineStr">
         <is>
           <t>Toutes valeurs en Ar</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="53" t="inlineStr">
+    <row r="13" ht="20.1" customHeight="1" s="74">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Validité du devis</t>
         </is>
       </c>
-      <c r="C13" s="54" t="n">
+      <c r="C13" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="D13" s="55" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>jours</t>
         </is>
       </c>
-      <c r="E13" s="56" t="inlineStr">
+      <c r="E13" s="101" t="inlineStr">
         <is>
           <t>Délai d'engagement du prix</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="53" t="inlineStr">
+    <row r="14" ht="20.1" customHeight="1" s="74">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Trajet par défaut</t>
         </is>
       </c>
-      <c r="C14" s="57" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>Aller-retour</t>
         </is>
       </c>
-      <c r="D14" s="55" t="inlineStr"/>
-      <c r="E14" s="56" t="inlineStr">
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="101" t="inlineStr">
         <is>
           <t>Le véhicule revient</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="53" t="inlineStr">
+    <row r="15" ht="20.1" customHeight="1" s="74">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Coefficient retour à vide</t>
         </is>
       </c>
-      <c r="C15" s="58" t="n">
+      <c r="C15" s="33" t="n">
         <v>0.7</v>
       </c>
-      <c r="D15" s="55" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="E15" s="56" t="inlineStr">
+      <c r="E15" s="101" t="inlineStr">
         <is>
           <t>0 = aller simple · 1 = retour plein</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="8" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+    <row r="16" ht="8.1" customHeight="1" s="74"/>
+    <row r="17" ht="21.95" customHeight="1" s="74">
+      <c r="B17" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⛽  PRIX DU CARBURANT  (modifiable selon le cours)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="59" t="inlineStr">
+    <row r="18" ht="20.1" customHeight="1" s="74">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Gasoil (diesel)</t>
         </is>
       </c>
-      <c r="C18" s="60" t="n">
+      <c r="C18" s="35" t="n">
         <v>4900</v>
       </c>
-      <c r="D18" s="61" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>/ litre</t>
         </is>
       </c>
-      <c r="E18" s="62" t="inlineStr">
+      <c r="E18" s="100" t="inlineStr">
         <is>
           <t>Tous les frais de carburant se recalculent à partir de cette valeur.</t>
         </is>
       </c>
-      <c r="F18" s="110" t="n"/>
-      <c r="G18" s="110" t="n"/>
-      <c r="H18" s="109" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="59" t="inlineStr">
+      <c r="F18" s="96" t="n"/>
+      <c r="G18" s="96" t="n"/>
+      <c r="H18" s="72" t="n"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" s="74">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Essence (sans plomb)</t>
         </is>
       </c>
-      <c r="C19" s="60" t="n">
+      <c r="C19" s="35" t="n">
         <v>5100</v>
       </c>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>/ litre</t>
         </is>
       </c>
-      <c r="E19" s="62" t="inlineStr">
+      <c r="E19" s="100" t="inlineStr">
         <is>
           <t>Tous les frais de carburant se recalculent à partir de cette valeur.</t>
         </is>
       </c>
-      <c r="F19" s="110" t="n"/>
-      <c r="G19" s="110" t="n"/>
-      <c r="H19" s="109" t="n"/>
-    </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="12" t="inlineStr">
+      <c r="F19" s="96" t="n"/>
+      <c r="G19" s="96" t="n"/>
+      <c r="H19" s="72" t="n"/>
+    </row>
+    <row r="20" ht="8.1" customHeight="1" s="74"/>
+    <row r="21" ht="21.95" customHeight="1" s="74">
+      <c r="B21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  🛣️  GRILLE TARIFAIRE KILOMÉTRIQUE  (tarif km HORS carburant + carburant par type)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="B22" s="63" t="inlineStr">
+    <row r="22" ht="26.1" customHeight="1" s="74">
+      <c r="B22" s="102" t="inlineStr">
         <is>
           <t>TYPE DE VÉHICULE</t>
         </is>
       </c>
-      <c r="C22" s="64" t="inlineStr">
+      <c r="C22" s="103" t="inlineStr">
         <is>
           <t>CAPACITÉ</t>
         </is>
       </c>
-      <c r="D22" s="64" t="inlineStr">
+      <c r="D22" s="103" t="inlineStr">
         <is>
           <t>TARIF/km
 (hors carburant)</t>
         </is>
       </c>
-      <c r="E22" s="64" t="inlineStr">
+      <c r="E22" s="103" t="inlineStr">
         <is>
           <t>CONSO
 (L/100km)</t>
         </is>
       </c>
-      <c r="F22" s="64" t="inlineStr">
+      <c r="F22" s="103" t="inlineStr">
         <is>
           <t>CARBURANT/km</t>
         </is>
       </c>
-      <c r="G22" s="64" t="inlineStr">
+      <c r="G22" s="103" t="inlineStr">
         <is>
           <t>FORFAIT BASE</t>
         </is>
       </c>
-      <c r="H22" s="64" t="inlineStr">
+      <c r="H22" s="103" t="inlineStr">
         <is>
           <t>MAJORATION</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
+    <row r="23" ht="18.95" customHeight="1" s="74">
+      <c r="B23" s="71" t="inlineStr">
         <is>
           <t>🛵 Moto-taxi / Tricycle</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="97" t="inlineStr">
         <is>
           <t>&lt; 200 kg</t>
         </is>
       </c>
-      <c r="D23" s="65" t="n">
+      <c r="D23" s="39" t="n">
         <v>800</v>
       </c>
-      <c r="E23" s="66" t="n">
+      <c r="E23" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="67">
+      <c r="F23" s="41">
         <f>ROUND(E23*$C$19/100,0)</f>
         <v/>
       </c>
-      <c r="G23" s="68" t="n">
+      <c r="G23" s="42" t="n">
         <v>15000</v>
       </c>
-      <c r="H23" s="69" t="n">
+      <c r="H23" s="43" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="B24" s="31" t="inlineStr">
+    <row r="24" ht="18.95" customHeight="1" s="74">
+      <c r="B24" s="76" t="inlineStr">
         <is>
           <t>🚐 Camionnette légère</t>
         </is>
       </c>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C24" s="94" t="inlineStr">
         <is>
           <t>200 – 800 kg</t>
         </is>
       </c>
-      <c r="D24" s="70" t="n">
+      <c r="D24" s="44" t="n">
         <v>1200</v>
       </c>
-      <c r="E24" s="71" t="n">
+      <c r="E24" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="F24" s="72">
+      <c r="F24" s="46">
         <f>ROUND(E24*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G24" s="73" t="n">
+      <c r="G24" s="47" t="n">
         <v>30000</v>
       </c>
-      <c r="H24" s="74" t="n">
+      <c r="H24" s="48" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="17" t="inlineStr">
+    <row r="25" ht="18.95" customHeight="1" s="74">
+      <c r="B25" s="71" t="inlineStr">
         <is>
           <t>🚚 Camion 3 tonnes</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="97" t="inlineStr">
         <is>
           <t>800 kg – 3 T</t>
         </is>
       </c>
-      <c r="D25" s="65" t="n">
+      <c r="D25" s="39" t="n">
         <v>1900</v>
       </c>
-      <c r="E25" s="66" t="n">
+      <c r="E25" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="F25" s="67">
+      <c r="F25" s="41">
         <f>ROUND(E25*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G25" s="68" t="n">
+      <c r="G25" s="42" t="n">
         <v>60000</v>
       </c>
-      <c r="H25" s="69" t="n">
+      <c r="H25" s="43" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="B26" s="31" t="inlineStr">
+    <row r="26" ht="18.95" customHeight="1" s="74">
+      <c r="B26" s="76" t="inlineStr">
         <is>
           <t>🚚 Camion 5 tonnes</t>
         </is>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C26" s="94" t="inlineStr">
         <is>
           <t>3 T – 5 T</t>
         </is>
       </c>
-      <c r="D26" s="70" t="n">
+      <c r="D26" s="44" t="n">
         <v>2800</v>
       </c>
-      <c r="E26" s="71" t="n">
+      <c r="E26" s="45" t="n">
         <v>25</v>
       </c>
-      <c r="F26" s="72">
+      <c r="F26" s="46">
         <f>ROUND(E26*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G26" s="73" t="n">
+      <c r="G26" s="47" t="n">
         <v>100000</v>
       </c>
-      <c r="H26" s="74" t="n">
+      <c r="H26" s="48" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="B27" s="17" t="inlineStr">
+    <row r="27" ht="18.95" customHeight="1" s="74">
+      <c r="B27" s="71" t="inlineStr">
         <is>
           <t>🚛 Camion 10 tonnes</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="97" t="inlineStr">
         <is>
           <t>5 T – 10 T</t>
         </is>
       </c>
-      <c r="D27" s="65" t="n">
+      <c r="D27" s="39" t="n">
         <v>3900</v>
       </c>
-      <c r="E27" s="66" t="n">
+      <c r="E27" s="40" t="n">
         <v>32</v>
       </c>
-      <c r="F27" s="67">
+      <c r="F27" s="41">
         <f>ROUND(E27*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G27" s="68" t="n">
+      <c r="G27" s="42" t="n">
         <v>180000</v>
       </c>
-      <c r="H27" s="69" t="n">
+      <c r="H27" s="43" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="B28" s="31" t="inlineStr">
+    <row r="28" ht="18.95" customHeight="1" s="74">
+      <c r="B28" s="76" t="inlineStr">
         <is>
           <t>🚛 Semi-remorque 20 T</t>
         </is>
       </c>
-      <c r="C28" s="30" t="inlineStr">
+      <c r="C28" s="94" t="inlineStr">
         <is>
           <t>10 T – 20 T</t>
         </is>
       </c>
-      <c r="D28" s="70" t="n">
+      <c r="D28" s="44" t="n">
         <v>5600</v>
       </c>
-      <c r="E28" s="71" t="n">
+      <c r="E28" s="45" t="n">
         <v>38</v>
       </c>
-      <c r="F28" s="72">
+      <c r="F28" s="46">
         <f>ROUND(E28*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G28" s="73" t="n">
+      <c r="G28" s="47" t="n">
         <v>300000</v>
       </c>
-      <c r="H28" s="74" t="n">
+      <c r="H28" s="48" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="B29" s="17" t="inlineStr">
+    <row r="29" ht="18.95" customHeight="1" s="74">
+      <c r="B29" s="71" t="inlineStr">
         <is>
           <t>❄️ Camion frigorifique 5 T</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="97" t="inlineStr">
         <is>
           <t>3 T – 5 T frigo</t>
         </is>
       </c>
-      <c r="D29" s="65" t="n">
+      <c r="D29" s="39" t="n">
         <v>3800</v>
       </c>
-      <c r="E29" s="66" t="n">
+      <c r="E29" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="F29" s="67">
+      <c r="F29" s="41">
         <f>ROUND(E29*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G29" s="68" t="n">
+      <c r="G29" s="42" t="n">
         <v>150000</v>
       </c>
-      <c r="H29" s="69" t="n">
+      <c r="H29" s="43" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="B30" s="31" t="inlineStr">
+    <row r="30" ht="18.95" customHeight="1" s="74">
+      <c r="B30" s="76" t="inlineStr">
         <is>
           <t>🚜 Camion benne</t>
         </is>
       </c>
-      <c r="C30" s="30" t="inlineStr">
+      <c r="C30" s="94" t="inlineStr">
         <is>
           <t>Jusqu'à 15 T</t>
         </is>
       </c>
-      <c r="D30" s="70" t="n">
+      <c r="D30" s="44" t="n">
         <v>4300</v>
       </c>
-      <c r="E30" s="71" t="n">
+      <c r="E30" s="45" t="n">
         <v>35</v>
       </c>
-      <c r="F30" s="72">
+      <c r="F30" s="46">
         <f>ROUND(E30*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G30" s="73" t="n">
+      <c r="G30" s="47" t="n">
         <v>200000</v>
       </c>
-      <c r="H30" s="74" t="n">
+      <c r="H30" s="48" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="B31" s="17" t="inlineStr">
+    <row r="31" ht="18.95" customHeight="1" s="74">
+      <c r="B31" s="71" t="inlineStr">
         <is>
           <t>📦 Conteneur 20 pieds</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="97" t="inlineStr">
         <is>
           <t>Max 24 T</t>
         </is>
       </c>
-      <c r="D31" s="65" t="n">
+      <c r="D31" s="39" t="n">
         <v>4600</v>
       </c>
-      <c r="E31" s="66" t="n">
+      <c r="E31" s="40" t="n">
         <v>38</v>
       </c>
-      <c r="F31" s="67">
+      <c r="F31" s="41">
         <f>ROUND(E31*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G31" s="68" t="n">
+      <c r="G31" s="42" t="n">
         <v>250000</v>
       </c>
-      <c r="H31" s="69" t="n">
+      <c r="H31" s="43" t="n">
         <v>0.35</v>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="B32" s="31" t="inlineStr">
+    <row r="32" ht="18.95" customHeight="1" s="74">
+      <c r="B32" s="76" t="inlineStr">
         <is>
           <t>📦 Conteneur 40 pieds</t>
         </is>
       </c>
-      <c r="C32" s="30" t="inlineStr">
+      <c r="C32" s="94" t="inlineStr">
         <is>
           <t>Max 28 T</t>
         </is>
       </c>
-      <c r="D32" s="70" t="n">
+      <c r="D32" s="44" t="n">
         <v>6300</v>
       </c>
-      <c r="E32" s="71" t="n">
+      <c r="E32" s="45" t="n">
         <v>45</v>
       </c>
-      <c r="F32" s="72">
+      <c r="F32" s="46">
         <f>ROUND(E32*$C$18/100,0)</f>
         <v/>
       </c>
-      <c r="G32" s="73" t="n">
+      <c r="G32" s="47" t="n">
         <v>400000</v>
       </c>
-      <c r="H32" s="74" t="n">
+      <c r="H32" s="48" t="n">
         <v>0.4</v>
       </c>
     </row>
-    <row r="33" ht="8" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="12" t="inlineStr">
+    <row r="33" ht="8.1" customHeight="1" s="74"/>
+    <row r="34" ht="21.95" customHeight="1" s="74">
+      <c r="B34" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  🗺️  ROUTES PRINCIPALES MADAGASCAR  (ALLER-RETOUR, général, carburant inclus)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="B35" s="63" t="inlineStr">
+    <row r="35" ht="26.1" customHeight="1" s="74">
+      <c r="B35" s="102" t="inlineStr">
         <is>
           <t>ROUTE</t>
         </is>
       </c>
-      <c r="C35" s="64" t="inlineStr">
+      <c r="C35" s="103" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="D35" s="64" t="inlineStr">
+      <c r="D35" s="103" t="inlineStr">
         <is>
           <t>CAMION 3T</t>
         </is>
       </c>
-      <c r="E35" s="64" t="inlineStr">
+      <c r="E35" s="103" t="inlineStr">
         <is>
           <t>CAMION 5T</t>
         </is>
       </c>
-      <c r="F35" s="64" t="inlineStr">
+      <c r="F35" s="103" t="inlineStr">
         <is>
           <t>SEMI-REM. 20T</t>
         </is>
       </c>
-      <c r="G35" s="64" t="inlineStr">
+      <c r="G35" s="103" t="inlineStr">
         <is>
           <t>DURÉE MOY.</t>
         </is>
       </c>
-      <c r="H35" s="109" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="17" t="inlineStr">
+      <c r="H35" s="72" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="74">
+      <c r="B36" s="71" t="inlineStr">
         <is>
           <t>Antananarivo → Toamasina</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="97" t="inlineStr">
         <is>
           <t>357 km</t>
         </is>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="12" t="n">
         <v>1921000</v>
       </c>
-      <c r="E36" s="75" t="n">
+      <c r="E36" s="49" t="n">
         <v>2883000</v>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="F36" s="12" t="n">
         <v>5848000</v>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G36" s="97" t="inlineStr">
         <is>
           <t>5h30</t>
         </is>
       </c>
-      <c r="H36" s="109" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="31" t="inlineStr">
+      <c r="H36" s="72" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="74">
+      <c r="B37" s="76" t="inlineStr">
         <is>
           <t>Antananarivo → Antsirabe</t>
         </is>
       </c>
-      <c r="C37" s="30" t="inlineStr">
+      <c r="C37" s="94" t="inlineStr">
         <is>
           <t>167 km</t>
         </is>
       </c>
-      <c r="D37" s="35" t="n">
+      <c r="D37" s="24" t="n">
         <v>931000</v>
       </c>
-      <c r="E37" s="76" t="n">
+      <c r="E37" s="50" t="n">
         <v>1402000</v>
       </c>
-      <c r="F37" s="35" t="n">
+      <c r="F37" s="24" t="n">
         <v>2895000</v>
       </c>
-      <c r="G37" s="30" t="inlineStr">
+      <c r="G37" s="94" t="inlineStr">
         <is>
           <t>3h00</t>
         </is>
       </c>
-      <c r="H37" s="109" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="17" t="inlineStr">
+      <c r="H37" s="72" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="74">
+      <c r="B38" s="71" t="inlineStr">
         <is>
           <t>Antananarivo → Mahajanga</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="97" t="inlineStr">
         <is>
           <t>472 km</t>
         </is>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="12" t="n">
         <v>2521000</v>
       </c>
-      <c r="E38" s="75" t="n">
+      <c r="E38" s="49" t="n">
         <v>3779000</v>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="F38" s="12" t="n">
         <v>7636000</v>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G38" s="97" t="inlineStr">
         <is>
           <t>8h00</t>
         </is>
       </c>
-      <c r="H38" s="109" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="31" t="inlineStr">
+      <c r="H38" s="72" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="74">
+      <c r="B39" s="76" t="inlineStr">
         <is>
           <t>Antananarivo → Fianarantsoa</t>
         </is>
       </c>
-      <c r="C39" s="30" t="inlineStr">
+      <c r="C39" s="94" t="inlineStr">
         <is>
           <t>404 km</t>
         </is>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="24" t="n">
         <v>2166000</v>
       </c>
-      <c r="E39" s="76" t="n">
+      <c r="E39" s="50" t="n">
         <v>3249000</v>
       </c>
-      <c r="F39" s="35" t="n">
+      <c r="F39" s="24" t="n">
         <v>6579000</v>
       </c>
-      <c r="G39" s="30" t="inlineStr">
+      <c r="G39" s="94" t="inlineStr">
         <is>
           <t>7h00</t>
         </is>
       </c>
-      <c r="H39" s="109" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="17" t="inlineStr">
+      <c r="H39" s="72" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="74">
+      <c r="B40" s="71" t="inlineStr">
         <is>
           <t>Antananarivo → Toliara</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="97" t="inlineStr">
         <is>
           <t>756 km</t>
         </is>
       </c>
-      <c r="D40" s="21" t="n">
+      <c r="D40" s="12" t="n">
         <v>4002000</v>
       </c>
-      <c r="E40" s="75" t="n">
+      <c r="E40" s="49" t="n">
         <v>5993000</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="F40" s="12" t="n">
         <v>12049000</v>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G40" s="97" t="inlineStr">
         <is>
           <t>13h00</t>
         </is>
       </c>
-      <c r="H40" s="109" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="31" t="inlineStr">
+      <c r="H40" s="72" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="74">
+      <c r="B41" s="76" t="inlineStr">
         <is>
           <t>Antananarivo → Ambositra</t>
         </is>
       </c>
-      <c r="C41" s="30" t="inlineStr">
+      <c r="C41" s="94" t="inlineStr">
         <is>
           <t>258 km</t>
         </is>
       </c>
-      <c r="D41" s="35" t="n">
+      <c r="D41" s="24" t="n">
         <v>1405000</v>
       </c>
-      <c r="E41" s="76" t="n">
+      <c r="E41" s="50" t="n">
         <v>2111000</v>
       </c>
-      <c r="F41" s="35" t="n">
+      <c r="F41" s="24" t="n">
         <v>4310000</v>
       </c>
-      <c r="G41" s="30" t="inlineStr">
+      <c r="G41" s="94" t="inlineStr">
         <is>
           <t>4h30</t>
         </is>
       </c>
-      <c r="H41" s="109" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="17" t="inlineStr">
+      <c r="H41" s="72" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="74">
+      <c r="B42" s="71" t="inlineStr">
         <is>
           <t>Antananarivo → Moramanga</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C42" s="97" t="inlineStr">
         <is>
           <t>109 km</t>
         </is>
       </c>
-      <c r="D42" s="21" t="n">
+      <c r="D42" s="12" t="n">
         <v>628000</v>
       </c>
-      <c r="E42" s="75" t="n">
+      <c r="E42" s="49" t="n">
         <v>950000</v>
       </c>
-      <c r="F42" s="21" t="n">
+      <c r="F42" s="12" t="n">
         <v>1994000</v>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G42" s="97" t="inlineStr">
         <is>
           <t>2h00</t>
         </is>
       </c>
-      <c r="H42" s="109" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="31" t="inlineStr">
+      <c r="H42" s="72" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="74">
+      <c r="B43" s="76" t="inlineStr">
         <is>
           <t>Antananarivo → Antalaha</t>
         </is>
       </c>
-      <c r="C43" s="30" t="inlineStr">
+      <c r="C43" s="94" t="inlineStr">
         <is>
           <t>820 km</t>
         </is>
       </c>
-      <c r="D43" s="35" t="n">
+      <c r="D43" s="24" t="n">
         <v>4335000</v>
       </c>
-      <c r="E43" s="76" t="n">
+      <c r="E43" s="50" t="n">
         <v>6491000</v>
       </c>
-      <c r="F43" s="35" t="n">
+      <c r="F43" s="24" t="n">
         <v>13044000</v>
       </c>
-      <c r="G43" s="30" t="inlineStr">
+      <c r="G43" s="94" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="H43" s="109" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="17" t="inlineStr">
+      <c r="H43" s="72" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="74">
+      <c r="B44" s="71" t="inlineStr">
         <is>
           <t>Antananarivo → Fort-Dauphin</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C44" s="97" t="inlineStr">
         <is>
           <t>950 km</t>
         </is>
       </c>
-      <c r="D44" s="21" t="n">
+      <c r="D44" s="12" t="n">
         <v>5013000</v>
       </c>
-      <c r="E44" s="75" t="n">
+      <c r="E44" s="49" t="n">
         <v>7505000</v>
       </c>
-      <c r="F44" s="21" t="n">
+      <c r="F44" s="12" t="n">
         <v>15064000</v>
       </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="G44" s="97" t="inlineStr">
         <is>
           <t>18h00</t>
         </is>
       </c>
-      <c r="H44" s="109" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="31" t="inlineStr">
+      <c r="H44" s="72" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="74">
+      <c r="B45" s="76" t="inlineStr">
         <is>
           <t>Toamasina → Mahajanga</t>
         </is>
       </c>
-      <c r="C45" s="30" t="inlineStr">
+      <c r="C45" s="94" t="inlineStr">
         <is>
           <t>720 km</t>
         </is>
       </c>
-      <c r="D45" s="35" t="n">
+      <c r="D45" s="24" t="n">
         <v>3814000</v>
       </c>
-      <c r="E45" s="76" t="n">
+      <c r="E45" s="50" t="n">
         <v>5712000</v>
       </c>
-      <c r="F45" s="35" t="n">
+      <c r="F45" s="24" t="n">
         <v>11490000</v>
       </c>
-      <c r="G45" s="30" t="inlineStr">
+      <c r="G45" s="94" t="inlineStr">
         <is>
           <t>14h00</t>
         </is>
       </c>
-      <c r="H45" s="109" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="B46" s="17" t="inlineStr">
+      <c r="H45" s="72" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="74">
+      <c r="B46" s="71" t="inlineStr">
         <is>
           <t>Antsirabe → Fianarantsoa</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C46" s="97" t="inlineStr">
         <is>
           <t>237 km</t>
         </is>
       </c>
-      <c r="D46" s="21" t="n">
+      <c r="D46" s="12" t="n">
         <v>1296000</v>
       </c>
-      <c r="E46" s="75" t="n">
+      <c r="E46" s="49" t="n">
         <v>1947000</v>
       </c>
-      <c r="F46" s="21" t="n">
+      <c r="F46" s="12" t="n">
         <v>3983000</v>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="G46" s="97" t="inlineStr">
         <is>
           <t>4h30</t>
         </is>
       </c>
-      <c r="H46" s="109" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="31" t="inlineStr">
+      <c r="H46" s="72" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="74">
+      <c r="B47" s="76" t="inlineStr">
         <is>
           <t>Mahajanga → Antsiranana</t>
         </is>
       </c>
-      <c r="C47" s="30" t="inlineStr">
+      <c r="C47" s="94" t="inlineStr">
         <is>
           <t>620 km</t>
         </is>
       </c>
-      <c r="D47" s="35" t="n">
+      <c r="D47" s="24" t="n">
         <v>3293000</v>
       </c>
-      <c r="E47" s="76" t="n">
+      <c r="E47" s="50" t="n">
         <v>4933000</v>
       </c>
-      <c r="F47" s="35" t="n">
+      <c r="F47" s="24" t="n">
         <v>9936000</v>
       </c>
-      <c r="G47" s="30" t="inlineStr">
+      <c r="G47" s="94" t="inlineStr">
         <is>
           <t>11h30</t>
         </is>
       </c>
-      <c r="H47" s="109" t="n"/>
-    </row>
-    <row r="48" ht="8" customHeight="1"/>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="12" t="inlineStr">
+      <c r="H47" s="72" t="n"/>
+    </row>
+    <row r="48" ht="8.1" customHeight="1" s="74"/>
+    <row r="49" ht="21.95" customHeight="1" s="74">
+      <c r="B49" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  📊  COEFFICIENTS DE MAJORATION  (marchandise / situation)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1">
-      <c r="B50" s="63" t="inlineStr">
+    <row r="50" ht="26.1" customHeight="1" s="74">
+      <c r="B50" s="102" t="inlineStr">
         <is>
           <t>TYPE / SITUATION</t>
         </is>
       </c>
-      <c r="C50" s="64" t="inlineStr">
+      <c r="C50" s="103" t="inlineStr">
         <is>
           <t>COEFF.</t>
         </is>
       </c>
-      <c r="D50" s="64" t="inlineStr">
+      <c r="D50" s="103" t="inlineStr">
         <is>
           <t>SURCHARGE</t>
         </is>
       </c>
-      <c r="E50" s="63" t="inlineStr">
+      <c r="E50" s="102" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="F50" s="110" t="n"/>
-      <c r="G50" s="110" t="n"/>
-      <c r="H50" s="109" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="B51" s="17" t="inlineStr">
+      <c r="F50" s="96" t="n"/>
+      <c r="G50" s="96" t="n"/>
+      <c r="H50" s="72" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="74">
+      <c r="B51" s="71" t="inlineStr">
         <is>
           <t>Marchandises générales (référence)</t>
         </is>
       </c>
-      <c r="C51" s="77" t="inlineStr">
+      <c r="C51" s="51" t="inlineStr">
         <is>
           <t>×1.00</t>
         </is>
       </c>
-      <c r="D51" s="68" t="n">
+      <c r="D51" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="78" t="inlineStr">
+      <c r="E51" s="95" t="inlineStr">
         <is>
           <t>Tarif de base</t>
         </is>
       </c>
-      <c r="F51" s="110" t="n"/>
-      <c r="G51" s="110" t="n"/>
-      <c r="H51" s="109" t="n"/>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="B52" s="31" t="inlineStr">
+      <c r="F51" s="96" t="n"/>
+      <c r="G51" s="96" t="n"/>
+      <c r="H51" s="72" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1" s="74">
+      <c r="B52" s="76" t="inlineStr">
         <is>
           <t>Produits périssables / alimentaires</t>
         </is>
       </c>
-      <c r="C52" s="79" t="inlineStr">
+      <c r="C52" s="53" t="inlineStr">
         <is>
           <t>×1.35</t>
         </is>
       </c>
-      <c r="D52" s="73" t="n">
+      <c r="D52" s="47" t="n">
         <v>20000</v>
       </c>
-      <c r="E52" s="80" t="inlineStr">
+      <c r="E52" s="98" t="inlineStr">
         <is>
           <t>Urgence + conditionnement</t>
         </is>
       </c>
-      <c r="F52" s="110" t="n"/>
-      <c r="G52" s="110" t="n"/>
-      <c r="H52" s="109" t="n"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="B53" s="17" t="inlineStr">
+      <c r="F52" s="96" t="n"/>
+      <c r="G52" s="96" t="n"/>
+      <c r="H52" s="72" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1" s="74">
+      <c r="B53" s="71" t="inlineStr">
         <is>
           <t>Marchandises fragiles / électroniques</t>
         </is>
       </c>
-      <c r="C53" s="77" t="inlineStr">
+      <c r="C53" s="51" t="inlineStr">
         <is>
           <t>×1.25</t>
         </is>
       </c>
-      <c r="D53" s="68" t="n">
+      <c r="D53" s="42" t="n">
         <v>15000</v>
       </c>
-      <c r="E53" s="78" t="inlineStr">
+      <c r="E53" s="95" t="inlineStr">
         <is>
           <t>Emballage soigné</t>
         </is>
       </c>
-      <c r="F53" s="110" t="n"/>
-      <c r="G53" s="110" t="n"/>
-      <c r="H53" s="109" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="31" t="inlineStr">
+      <c r="F53" s="96" t="n"/>
+      <c r="G53" s="96" t="n"/>
+      <c r="H53" s="72" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="74">
+      <c r="B54" s="76" t="inlineStr">
         <is>
           <t>Matériaux lourds (ciment, ferraille)</t>
         </is>
       </c>
-      <c r="C54" s="79" t="inlineStr">
+      <c r="C54" s="53" t="inlineStr">
         <is>
           <t>×1.15</t>
         </is>
       </c>
-      <c r="D54" s="73" t="n">
+      <c r="D54" s="47" t="n">
         <v>10000</v>
       </c>
-      <c r="E54" s="80" t="inlineStr">
+      <c r="E54" s="98" t="inlineStr">
         <is>
           <t>Renforcement camion</t>
         </is>
       </c>
-      <c r="F54" s="110" t="n"/>
-      <c r="G54" s="110" t="n"/>
-      <c r="H54" s="109" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="17" t="inlineStr">
+      <c r="F54" s="96" t="n"/>
+      <c r="G54" s="96" t="n"/>
+      <c r="H54" s="72" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1" s="74">
+      <c r="B55" s="71" t="inlineStr">
         <is>
           <t>Produits dangereux (ADR homologués)</t>
         </is>
       </c>
-      <c r="C55" s="77" t="inlineStr">
+      <c r="C55" s="51" t="inlineStr">
         <is>
           <t>×1.80</t>
         </is>
       </c>
-      <c r="D55" s="68" t="n">
+      <c r="D55" s="42" t="n">
         <v>50000</v>
       </c>
-      <c r="E55" s="78" t="inlineStr">
+      <c r="E55" s="95" t="inlineStr">
         <is>
           <t>Conformité réglementaire</t>
         </is>
       </c>
-      <c r="F55" s="110" t="n"/>
-      <c r="G55" s="110" t="n"/>
-      <c r="H55" s="109" t="n"/>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="B56" s="31" t="inlineStr">
+      <c r="F55" s="96" t="n"/>
+      <c r="G55" s="96" t="n"/>
+      <c r="H55" s="72" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1" s="74">
+      <c r="B56" s="76" t="inlineStr">
         <is>
           <t>Conteneur chargé (FCL)</t>
         </is>
       </c>
-      <c r="C56" s="79" t="inlineStr">
+      <c r="C56" s="53" t="inlineStr">
         <is>
           <t>×2.10</t>
         </is>
       </c>
-      <c r="D56" s="73" t="n">
+      <c r="D56" s="47" t="n">
         <v>80000</v>
       </c>
-      <c r="E56" s="80" t="inlineStr">
+      <c r="E56" s="98" t="inlineStr">
         <is>
           <t>Équipement spécial</t>
         </is>
       </c>
-      <c r="F56" s="110" t="n"/>
-      <c r="G56" s="110" t="n"/>
-      <c r="H56" s="109" t="n"/>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="17" t="inlineStr">
+      <c r="F56" s="96" t="n"/>
+      <c r="G56" s="96" t="n"/>
+      <c r="H56" s="72" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1" s="74">
+      <c r="B57" s="71" t="inlineStr">
         <is>
           <t>Convoi exceptionnel (&gt;48T)</t>
         </is>
       </c>
-      <c r="C57" s="77" t="inlineStr">
+      <c r="C57" s="51" t="inlineStr">
         <is>
           <t>×3.00</t>
         </is>
       </c>
-      <c r="D57" s="68" t="n">
+      <c r="D57" s="42" t="n">
         <v>120000</v>
       </c>
-      <c r="E57" s="78" t="inlineStr">
+      <c r="E57" s="95" t="inlineStr">
         <is>
           <t>Escorte police obligatoire</t>
         </is>
       </c>
-      <c r="F57" s="110" t="n"/>
-      <c r="G57" s="110" t="n"/>
-      <c r="H57" s="109" t="n"/>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="31" t="inlineStr">
+      <c r="F57" s="96" t="n"/>
+      <c r="G57" s="96" t="n"/>
+      <c r="H57" s="72" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1" s="74">
+      <c r="B58" s="76" t="inlineStr">
         <is>
           <t>Animaux vivants</t>
         </is>
       </c>
-      <c r="C58" s="79" t="inlineStr">
+      <c r="C58" s="53" t="inlineStr">
         <is>
           <t>×1.60</t>
         </is>
       </c>
-      <c r="D58" s="73" t="n">
+      <c r="D58" s="47" t="n">
         <v>35000</v>
       </c>
-      <c r="E58" s="80" t="inlineStr">
+      <c r="E58" s="98" t="inlineStr">
         <is>
           <t>Conditions spéciales</t>
         </is>
       </c>
-      <c r="F58" s="110" t="n"/>
-      <c r="G58" s="110" t="n"/>
-      <c r="H58" s="109" t="n"/>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="17" t="inlineStr">
+      <c r="F58" s="96" t="n"/>
+      <c r="G58" s="96" t="n"/>
+      <c r="H58" s="72" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1" s="74">
+      <c r="B59" s="71" t="inlineStr">
         <is>
           <t>Service express (J+1)</t>
         </is>
       </c>
-      <c r="C59" s="77" t="inlineStr">
+      <c r="C59" s="51" t="inlineStr">
         <is>
           <t>+30%</t>
         </is>
       </c>
-      <c r="D59" s="68" t="n">
+      <c r="D59" s="42" t="n">
         <v>25000</v>
       </c>
-      <c r="E59" s="78" t="inlineStr">
+      <c r="E59" s="95" t="inlineStr">
         <is>
           <t>Majoration urgence</t>
         </is>
       </c>
-      <c r="F59" s="110" t="n"/>
-      <c r="G59" s="110" t="n"/>
-      <c r="H59" s="109" t="n"/>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="31" t="inlineStr">
+      <c r="F59" s="96" t="n"/>
+      <c r="G59" s="96" t="n"/>
+      <c r="H59" s="72" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1" s="74">
+      <c r="B60" s="76" t="inlineStr">
         <is>
           <t>Livraison de nuit (22h-6h)</t>
         </is>
       </c>
-      <c r="C60" s="79" t="inlineStr">
+      <c r="C60" s="53" t="inlineStr">
         <is>
           <t>+20%</t>
         </is>
       </c>
-      <c r="D60" s="73" t="n">
+      <c r="D60" s="47" t="n">
         <v>18000</v>
       </c>
-      <c r="E60" s="80" t="inlineStr">
+      <c r="E60" s="98" t="inlineStr">
         <is>
           <t>Majoration horaire</t>
         </is>
       </c>
-      <c r="F60" s="110" t="n"/>
-      <c r="G60" s="110" t="n"/>
-      <c r="H60" s="109" t="n"/>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="B61" s="17" t="inlineStr">
+      <c r="F60" s="96" t="n"/>
+      <c r="G60" s="96" t="n"/>
+      <c r="H60" s="72" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1" s="74">
+      <c r="B61" s="71" t="inlineStr">
         <is>
           <t>Zones rurales / pistes dégradées</t>
         </is>
       </c>
-      <c r="C61" s="77" t="inlineStr">
+      <c r="C61" s="51" t="inlineStr">
         <is>
           <t>+25%</t>
         </is>
       </c>
-      <c r="D61" s="68" t="n">
+      <c r="D61" s="42" t="n">
         <v>22000</v>
       </c>
-      <c r="E61" s="78" t="inlineStr">
+      <c r="E61" s="95" t="inlineStr">
         <is>
           <t>Usure + surconsommation</t>
         </is>
       </c>
-      <c r="F61" s="110" t="n"/>
-      <c r="G61" s="110" t="n"/>
-      <c r="H61" s="109" t="n"/>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="31" t="inlineStr">
+      <c r="F61" s="96" t="n"/>
+      <c r="G61" s="96" t="n"/>
+      <c r="H61" s="72" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1" s="74">
+      <c r="B62" s="76" t="inlineStr">
         <is>
           <t>Transport frigorifique</t>
         </is>
       </c>
-      <c r="C62" s="79" t="inlineStr">
+      <c r="C62" s="53" t="inlineStr">
         <is>
           <t>+40%</t>
         </is>
       </c>
-      <c r="D62" s="73" t="n">
+      <c r="D62" s="47" t="n">
         <v>45000</v>
       </c>
-      <c r="E62" s="80" t="inlineStr">
+      <c r="E62" s="98" t="inlineStr">
         <is>
           <t>Groupe froid (carburant compté à part)</t>
         </is>
       </c>
-      <c r="F62" s="110" t="n"/>
-      <c r="G62" s="110" t="n"/>
-      <c r="H62" s="109" t="n"/>
+      <c r="F62" s="96" t="n"/>
+      <c r="G62" s="96" t="n"/>
+      <c r="H62" s="72" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -4008,32 +3614,32 @@
     <mergeCell ref="B34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E07B20"/>
+    <tabColor rgb="FFE07B20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" style="74" min="1" max="1"/>
+    <col width="38" customWidth="1" style="74" min="2" max="2"/>
+    <col width="22" customWidth="1" style="74" min="3" max="3"/>
+    <col width="18" customWidth="1" style="74" min="4" max="4"/>
+    <col width="6" customWidth="1" style="74" min="5" max="5"/>
+    <col width="16" customWidth="1" style="74" min="6" max="6"/>
+    <col width="14" customWidth="1" style="74" min="7" max="7"/>
+    <col width="3" customWidth="1" style="74" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="81" t="inlineStr">
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>🧮  CALCULATEUR DE PRIX RAPIDE — ONE WAY</t>
         </is>
@@ -4042,322 +3648,322 @@
     <row r="3"/>
     <row r="4"/>
     <row r="5"/>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+    <row r="6" ht="8.1" customHeight="1" s="74"/>
+    <row r="8" ht="21.95" customHeight="1" s="74">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  📝  PARAMÈTRES DE LA DEMANDE</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="B9" s="53" t="inlineStr">
+    <row r="9" ht="21" customHeight="1" s="74">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Distance du trajet — aller (km)</t>
         </is>
       </c>
-      <c r="C9" s="82" t="n">
+      <c r="C9" s="55" t="n">
         <v>357</v>
       </c>
-      <c r="D9" s="55" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>km</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Véhicule :</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="21" customHeight="1">
-      <c r="B10" s="53" t="inlineStr">
+    <row r="10" ht="21" customHeight="1" s="74">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Type véhicule (1=Moto → 10=Cont40')</t>
         </is>
       </c>
-      <c r="C10" s="82" t="n">
+      <c r="C10" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="55" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>1 à 10</t>
         </is>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="108">
         <f>INDEX('⚙️ Paramètres'!$B$23:$B$32,C10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="53" t="inlineStr">
+    <row r="11" ht="21" customHeight="1" s="74">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Poids de la marchandise</t>
         </is>
       </c>
-      <c r="C11" s="82" t="n">
+      <c r="C11" s="55" t="n">
         <v>4000</v>
       </c>
-      <c r="D11" s="55" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="B12" s="53" t="inlineStr">
+    <row r="12" ht="21" customHeight="1" s="74">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Valeur déclarée marchandise</t>
         </is>
       </c>
-      <c r="C12" s="83" t="n">
+      <c r="C12" s="56" t="n">
         <v>20000000</v>
       </c>
-      <c r="D12" s="55" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>Ar</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="53" t="inlineStr">
+    <row r="13" ht="21" customHeight="1" s="74">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Manutention chargement ?</t>
         </is>
       </c>
-      <c r="C13" s="82" t="inlineStr">
+      <c r="C13" s="55" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="D13" s="55" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>Oui/Non</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="53" t="inlineStr">
+    <row r="14" ht="21" customHeight="1" s="74">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Manutention déchargement ?</t>
         </is>
       </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="C14" s="55" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="D14" s="55" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>Oui/Non</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="B15" s="53" t="inlineStr">
+    <row r="15" ht="21" customHeight="1" s="74">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Aller-retour ?</t>
         </is>
       </c>
-      <c r="C15" s="82" t="inlineStr">
+      <c r="C15" s="55" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="D15" s="55" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>Oui/Non</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="B16" s="53" t="inlineStr">
+    <row r="16" ht="21" customHeight="1" s="74">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Remise à appliquer</t>
         </is>
       </c>
-      <c r="C16" s="82" t="n">
+      <c r="C16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="55" t="inlineStr">
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="53" t="inlineStr">
+    <row r="17" ht="21" customHeight="1" s="74">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>TVA ?</t>
         </is>
       </c>
-      <c r="C17" s="82" t="inlineStr">
+      <c r="C17" s="55" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="D17" s="55" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>Oui/Non</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="8" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+    <row r="18" ht="8.1" customHeight="1" s="74"/>
+    <row r="19" ht="21.95" customHeight="1" s="74">
+      <c r="B19" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  💰  RÉSULTAT DU CALCUL AUTOMATIQUE</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+    <row r="20" ht="20.1" customHeight="1" s="74">
+      <c r="B20" s="71" t="inlineStr">
         <is>
           <t>Frais kilométriques aller (hors carburant)</t>
         </is>
       </c>
-      <c r="C20" s="84">
+      <c r="C20" s="104">
         <f>ROUND(C9*INDEX('⚙️ Paramètres'!$D$23:$D$32,C10)*(1+INDEX('⚙️ Paramètres'!$H$23:$H$32,C10)),0)</f>
         <v/>
       </c>
-      <c r="D20" s="109" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="24" t="inlineStr">
+      <c r="D20" s="72" t="n"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" s="74">
+      <c r="B21" s="86" t="inlineStr">
         <is>
           <t>Carburant aller (selon type de véhicule)</t>
         </is>
       </c>
-      <c r="C21" s="85">
+      <c r="C21" s="105">
         <f>ROUND(C9*INDEX('⚙️ Paramètres'!$F$23:$F$32,C10),0)</f>
         <v/>
       </c>
-      <c r="D21" s="109" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="24" t="inlineStr">
+      <c r="D21" s="72" t="n"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" s="74">
+      <c r="B22" s="86" t="inlineStr">
         <is>
           <t>Retour véhicule à vide (repositionnement)</t>
         </is>
       </c>
-      <c r="C22" s="85">
+      <c r="C22" s="105">
         <f>IF(C15="Oui",ROUND((C20+C21)*'⚙️ Paramètres'!$C$15,0),0)</f>
         <v/>
       </c>
-      <c r="D22" s="109" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="31" t="inlineStr">
+      <c r="D22" s="72" t="n"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" s="74">
+      <c r="B23" s="76" t="inlineStr">
         <is>
           <t>Forfait de base véhicule</t>
         </is>
       </c>
-      <c r="C23" s="86">
+      <c r="C23" s="109">
         <f>INDEX('⚙️ Paramètres'!$G$23:$G$32,C10)</f>
         <v/>
       </c>
-      <c r="D23" s="109" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="D23" s="72" t="n"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" s="74">
+      <c r="B24" s="71" t="inlineStr">
         <is>
           <t>Manutention chargement</t>
         </is>
       </c>
-      <c r="C24" s="84">
+      <c r="C24" s="104">
         <f>IF(C13="Oui",ROUND(INDEX('⚙️ Paramètres'!$G$23:$G$32,C10)*0.15,0),0)</f>
         <v/>
       </c>
-      <c r="D24" s="109" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="31" t="inlineStr">
+      <c r="D24" s="72" t="n"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" s="74">
+      <c r="B25" s="76" t="inlineStr">
         <is>
           <t>Manutention déchargement</t>
         </is>
       </c>
-      <c r="C25" s="86">
+      <c r="C25" s="109">
         <f>IF(C14="Oui",ROUND(INDEX('⚙️ Paramètres'!$G$23:$G$32,C10)*0.15,0),0)</f>
         <v/>
       </c>
-      <c r="D25" s="109" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="17" t="inlineStr">
+      <c r="D25" s="72" t="n"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" s="74">
+      <c r="B26" s="71" t="inlineStr">
         <is>
           <t>Assurance (0,5% valeur déclarée)</t>
         </is>
       </c>
-      <c r="C26" s="84">
+      <c r="C26" s="104">
         <f>ROUND(C12*0.005,0)</f>
         <v/>
       </c>
-      <c r="D26" s="109" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="31" t="inlineStr">
+      <c r="D26" s="72" t="n"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" s="74">
+      <c r="B27" s="76" t="inlineStr">
         <is>
           <t>Frais divers (péages, 3% du transport)</t>
         </is>
       </c>
-      <c r="C27" s="86">
+      <c r="C27" s="109">
         <f>ROUND((C20+C22)*0.03,0)</f>
         <v/>
       </c>
-      <c r="D27" s="109" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="87" t="inlineStr">
+      <c r="D27" s="72" t="n"/>
+    </row>
+    <row r="28" ht="21.95" customHeight="1" s="74">
+      <c r="B28" s="57" t="inlineStr">
         <is>
           <t>SOUS-TOTAL H.T.</t>
         </is>
       </c>
-      <c r="C28" s="88">
+      <c r="C28" s="111">
         <f>SUM(C20:C27)</f>
         <v/>
       </c>
-      <c r="D28" s="109" t="n"/>
+      <c r="D28" s="72" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="90" t="inlineStr">
+      <c r="B29" s="58" t="inlineStr">
         <is>
           <t>Remise commerciale</t>
         </is>
       </c>
-      <c r="C29" s="42">
+      <c r="C29" s="84">
         <f>-ROUND(C28*C16/100,0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="90" t="inlineStr">
+      <c r="B30" s="58" t="inlineStr">
         <is>
           <t>TVA 20% (si applicable)</t>
         </is>
       </c>
-      <c r="C30" s="91">
+      <c r="C30" s="106">
         <f>IF(C17="Oui",ROUND((C28+C29)*0.2,0),0)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="92" t="inlineStr">
+    <row r="31" ht="30" customHeight="1" s="74">
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>💰  TOTAL ESTIMÉ TTC</t>
         </is>
       </c>
-      <c r="C31" s="93">
+      <c r="C31" s="112">
         <f>C28+C29+C30</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="90" t="inlineStr">
+    <row r="32" ht="20.1" customHeight="1" s="74">
+      <c r="B32" s="58" t="inlineStr">
         <is>
           <t>Prix moyen / km (aller)</t>
         </is>
       </c>
-      <c r="C32" s="94">
+      <c r="C32" s="110">
         <f>IF(C9&gt;0,ROUND(C31/C9,0),0)</f>
         <v/>
       </c>
@@ -4367,13 +3973,13 @@
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B2:G5"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="C28:D28"/>
@@ -4386,43 +3992,41 @@
     <dataValidation sqref="C13 C14 C15 C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
-    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Type de véhicule" error="Choisir un type de véhicule de 1 (moto) à 10 (conteneur 40')." type="whole" operator="between">
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Type de véhicule" error="Choisir un type de véhicule de 1 (moto) à 10 (conteneur 40')." type="whole">
       <formula1>1</formula1>
       <formula2>10</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C86A10"/>
+    <tabColor rgb="FFC86A10"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:L21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="3" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" style="74" min="1" max="1"/>
+    <col width="16" customWidth="1" style="74" min="2" max="2"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="24" customWidth="1" style="74" min="4" max="4"/>
+    <col width="18" customWidth="1" style="74" min="5" max="6"/>
+    <col width="11" customWidth="1" style="74" min="7" max="7"/>
+    <col width="16" customWidth="1" style="74" min="8" max="8"/>
+    <col width="14" customWidth="1" style="74" min="9" max="10"/>
+    <col width="13" customWidth="1" style="74" min="11" max="11"/>
+    <col width="18" customWidth="1" style="74" min="12" max="12"/>
+    <col width="3" customWidth="1" style="74" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="95" t="inlineStr">
+      <c r="B2" s="115" t="inlineStr">
         <is>
           <t>📊  HISTORIQUE DES DEVIS — ONE WAY (aller-retour)</t>
         </is>
@@ -4430,510 +4034,510 @@
     </row>
     <row r="3"/>
     <row r="4"/>
-    <row r="5" ht="8" customHeight="1"/>
-    <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="64" t="inlineStr">
+    <row r="5" ht="8.1" customHeight="1" s="74"/>
+    <row r="6" ht="26.1" customHeight="1" s="74">
+      <c r="B6" s="103" t="inlineStr">
         <is>
           <t>N° DEVIS</t>
         </is>
       </c>
-      <c r="C6" s="64" t="inlineStr">
+      <c r="C6" s="103" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="D6" s="63" t="inlineStr">
+      <c r="D6" s="102" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
       </c>
-      <c r="E6" s="63" t="inlineStr">
+      <c r="E6" s="102" t="inlineStr">
         <is>
           <t>DÉPART</t>
         </is>
       </c>
-      <c r="F6" s="63" t="inlineStr">
+      <c r="F6" s="102" t="inlineStr">
         <is>
           <t>ARRIVÉE</t>
         </is>
       </c>
-      <c r="G6" s="64" t="inlineStr">
+      <c r="G6" s="103" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H6" s="63" t="inlineStr">
+      <c r="H6" s="102" t="inlineStr">
         <is>
           <t>VÉHICULE</t>
         </is>
       </c>
-      <c r="I6" s="64" t="inlineStr">
+      <c r="I6" s="103" t="inlineStr">
         <is>
           <t>HT (Ar)</t>
         </is>
       </c>
-      <c r="J6" s="64" t="inlineStr">
+      <c r="J6" s="103" t="inlineStr">
         <is>
           <t>TTC (Ar)</t>
         </is>
       </c>
-      <c r="K6" s="64" t="inlineStr">
+      <c r="K6" s="103" t="inlineStr">
         <is>
           <t>STATUT</t>
         </is>
       </c>
-      <c r="L6" s="63" t="inlineStr">
+      <c r="L6" s="102" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="B7" s="77" t="inlineStr">
+    <row r="7" ht="18.95" customHeight="1" s="74">
+      <c r="B7" s="51" t="inlineStr">
         <is>
           <t>OW-0001</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="71" t="inlineStr">
         <is>
           <t>Société ABC Import</t>
         </is>
       </c>
-      <c r="E7" s="97" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>Analakely, Tanà</t>
         </is>
       </c>
-      <c r="F7" s="97" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>Toamasina Port</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="97" t="inlineStr">
         <is>
           <t>357 km</t>
         </is>
       </c>
-      <c r="H7" s="98" t="inlineStr">
+      <c r="H7" s="61" t="inlineStr">
         <is>
           <t>Camion 5T</t>
         </is>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="12" t="n">
         <v>2883000</v>
       </c>
-      <c r="J7" s="75" t="n">
+      <c r="J7" s="49" t="n">
         <v>2883000</v>
       </c>
-      <c r="K7" s="99" t="inlineStr">
+      <c r="K7" s="62" t="inlineStr">
         <is>
           <t>✅ Accepté</t>
         </is>
       </c>
-      <c r="L7" s="78" t="inlineStr">
+      <c r="L7" s="95" t="inlineStr">
         <is>
           <t>Livraison OK</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="19" customHeight="1">
-      <c r="B8" s="79" t="inlineStr">
+    <row r="8" ht="18.95" customHeight="1" s="74">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>OW-0002</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="94" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="76" t="inlineStr">
         <is>
           <t>Marie Rakoto</t>
         </is>
       </c>
-      <c r="E8" s="100" t="inlineStr">
+      <c r="E8" s="63" t="inlineStr">
         <is>
           <t>Ivandry, Tanà</t>
         </is>
       </c>
-      <c r="F8" s="100" t="inlineStr">
+      <c r="F8" s="63" t="inlineStr">
         <is>
           <t>Antsirabe Centre</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="G8" s="94" t="inlineStr">
         <is>
           <t>167 km</t>
         </is>
       </c>
-      <c r="H8" s="101" t="inlineStr">
+      <c r="H8" s="64" t="inlineStr">
         <is>
           <t>Camionnette</t>
         </is>
       </c>
-      <c r="I8" s="35" t="n">
+      <c r="I8" s="24" t="n">
         <v>931000</v>
       </c>
-      <c r="J8" s="76" t="n">
+      <c r="J8" s="50" t="n">
         <v>931000</v>
       </c>
-      <c r="K8" s="102" t="inlineStr">
+      <c r="K8" s="65" t="inlineStr">
         <is>
           <t>✅ Accepté</t>
         </is>
       </c>
-      <c r="L8" s="80" t="inlineStr">
+      <c r="L8" s="98" t="inlineStr">
         <is>
           <t>Marchandises générales</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="B9" s="77" t="inlineStr">
+    <row r="9" ht="18.95" customHeight="1" s="74">
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>OW-0003</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="71" t="inlineStr">
         <is>
           <t>Export Mada SARL</t>
         </is>
       </c>
-      <c r="E9" s="97" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>Tsaralalàna</t>
         </is>
       </c>
-      <c r="F9" s="97" t="inlineStr">
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>Mahajanga Port</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="97" t="inlineStr">
         <is>
           <t>472 km</t>
         </is>
       </c>
-      <c r="H9" s="98" t="inlineStr">
+      <c r="H9" s="61" t="inlineStr">
         <is>
           <t>Camion 5T</t>
         </is>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="12" t="n">
         <v>3779000</v>
       </c>
-      <c r="J9" s="75" t="n">
+      <c r="J9" s="49" t="n">
         <v>3779000</v>
       </c>
-      <c r="K9" s="99" t="inlineStr">
+      <c r="K9" s="62" t="inlineStr">
         <is>
           <t>✅ Accepté</t>
         </is>
       </c>
-      <c r="L9" s="78" t="inlineStr">
+      <c r="L9" s="95" t="inlineStr">
         <is>
           <t>Périssables urgents</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="B10" s="79" t="inlineStr">
+    <row r="10" ht="18.95" customHeight="1" s="74">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>OW-0004</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="94" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="D10" s="31" t="inlineStr">
+      <c r="D10" s="76" t="inlineStr">
         <is>
           <t>Fara Rasolofo</t>
         </is>
       </c>
-      <c r="E10" s="100" t="inlineStr">
+      <c r="E10" s="63" t="inlineStr">
         <is>
           <t>67 Ha, Tanà</t>
         </is>
       </c>
-      <c r="F10" s="100" t="inlineStr">
+      <c r="F10" s="63" t="inlineStr">
         <is>
           <t>Fianarantsoa</t>
         </is>
       </c>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="G10" s="94" t="inlineStr">
         <is>
           <t>404 km</t>
         </is>
       </c>
-      <c r="H10" s="101" t="inlineStr">
+      <c r="H10" s="64" t="inlineStr">
         <is>
           <t>Semi-remorque</t>
         </is>
       </c>
-      <c r="I10" s="35" t="n">
+      <c r="I10" s="24" t="n">
         <v>6579000</v>
       </c>
-      <c r="J10" s="76" t="n">
+      <c r="J10" s="50" t="n">
         <v>6579000</v>
       </c>
-      <c r="K10" s="102" t="inlineStr">
+      <c r="K10" s="65" t="inlineStr">
         <is>
           <t>✅ Accepté</t>
         </is>
       </c>
-      <c r="L10" s="80" t="inlineStr">
+      <c r="L10" s="98" t="inlineStr">
         <is>
           <t>Semi-remorque</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="B11" s="77" t="inlineStr">
+    <row r="11" ht="18.95" customHeight="1" s="74">
+      <c r="B11" s="51" t="inlineStr">
         <is>
           <t>OW-0005</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="71" t="inlineStr">
         <is>
           <t>Solo Andria</t>
         </is>
       </c>
-      <c r="E11" s="97" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>Ambohimangakely</t>
         </is>
       </c>
-      <c r="F11" s="97" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>Moramanga</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="97" t="inlineStr">
         <is>
           <t>109 km</t>
         </is>
       </c>
-      <c r="H11" s="98" t="inlineStr">
+      <c r="H11" s="61" t="inlineStr">
         <is>
           <t>Moto-tricycle</t>
         </is>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="12" t="n">
         <v>365000</v>
       </c>
-      <c r="J11" s="75" t="n">
+      <c r="J11" s="49" t="n">
         <v>365000</v>
       </c>
-      <c r="K11" s="99" t="inlineStr">
+      <c r="K11" s="62" t="inlineStr">
         <is>
           <t>⏳ En attente</t>
         </is>
       </c>
-      <c r="L11" s="78" t="inlineStr">
+      <c r="L11" s="95" t="inlineStr">
         <is>
           <t>En cours</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="B12" s="79" t="inlineStr">
+    <row r="12" ht="18.95" customHeight="1" s="74">
+      <c r="B12" s="53" t="inlineStr">
         <is>
           <t>OW-0006</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
         <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="D12" s="31" t="inlineStr">
+      <c r="D12" s="76" t="inlineStr">
         <is>
           <t>Haja Rabe</t>
         </is>
       </c>
-      <c r="E12" s="100" t="inlineStr">
+      <c r="E12" s="63" t="inlineStr">
         <is>
           <t>Port Toamasina</t>
         </is>
       </c>
-      <c r="F12" s="100" t="inlineStr">
+      <c r="F12" s="63" t="inlineStr">
         <is>
           <t>Ambositra</t>
         </is>
       </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="G12" s="94" t="inlineStr">
         <is>
           <t>460 km</t>
         </is>
       </c>
-      <c r="H12" s="101" t="inlineStr">
+      <c r="H12" s="64" t="inlineStr">
         <is>
           <t>Camion 5T</t>
         </is>
       </c>
-      <c r="I12" s="35" t="n">
+      <c r="I12" s="24" t="n">
         <v>3685000</v>
       </c>
-      <c r="J12" s="76" t="n">
+      <c r="J12" s="50" t="n">
         <v>3685000</v>
       </c>
-      <c r="K12" s="102" t="inlineStr">
+      <c r="K12" s="65" t="inlineStr">
         <is>
           <t>❌ Refusé</t>
         </is>
       </c>
-      <c r="L12" s="80" t="inlineStr">
+      <c r="L12" s="98" t="inlineStr">
         <is>
           <t>Prix refusé</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="B13" s="77" t="inlineStr">
+    <row r="13" ht="18.95" customHeight="1" s="74">
+      <c r="B13" s="51" t="inlineStr">
         <is>
           <t>OW-0007</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>Tanà Distribution</t>
         </is>
       </c>
-      <c r="E13" s="97" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>Analakely, Tanà</t>
         </is>
       </c>
-      <c r="F13" s="97" t="inlineStr">
+      <c r="F13" s="60" t="inlineStr">
         <is>
           <t>Antsirabe</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="97" t="inlineStr">
         <is>
           <t>167 km</t>
         </is>
       </c>
-      <c r="H13" s="98" t="inlineStr">
+      <c r="H13" s="61" t="inlineStr">
         <is>
           <t>Camionnette</t>
         </is>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="12" t="n">
         <v>931000</v>
       </c>
-      <c r="J13" s="75" t="n">
+      <c r="J13" s="49" t="n">
         <v>931000</v>
       </c>
-      <c r="K13" s="99" t="inlineStr">
+      <c r="K13" s="62" t="inlineStr">
         <is>
           <t>⏳ En attente</t>
         </is>
       </c>
-      <c r="L13" s="78" t="inlineStr">
+      <c r="L13" s="95" t="inlineStr">
         <is>
           <t>Devis émis</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="103" t="inlineStr">
+    <row r="14" ht="21.95" customHeight="1" s="74">
+      <c r="B14" s="114" t="inlineStr">
         <is>
           <t>TOTAL (devis acceptés)</t>
         </is>
       </c>
-      <c r="I14" s="104">
+      <c r="I14" s="67">
         <f>SUMIF(K7:K13,"✅ Accepté",I7:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="103">
+      <c r="J14" s="114">
         <f>COUNTIF(K7:K13,"✅ Accepté")&amp;" acceptés"</f>
         <v/>
       </c>
-      <c r="K14" s="46" t="n"/>
-      <c r="L14" s="46" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="105" t="inlineStr">
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="28" t="n"/>
+    </row>
+    <row r="16" ht="21.95" customHeight="1" s="74">
+      <c r="B16" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">  📈  STATISTIQUES RAPIDES</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="B17" s="53" t="inlineStr">
+    <row r="17" ht="18.95" customHeight="1" s="74">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Devis émis</t>
         </is>
       </c>
-      <c r="C17" s="106">
+      <c r="C17" s="68">
         <f>COUNTA(B7:B13)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="B18" s="53" t="inlineStr">
+    <row r="18" ht="18.95" customHeight="1" s="74">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Devis acceptés</t>
         </is>
       </c>
-      <c r="C18" s="106">
+      <c r="C18" s="68">
         <f>COUNTIF(K7:K13,"✅ Accepté")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="B19" s="53" t="inlineStr">
+    <row r="19" ht="18.95" customHeight="1" s="74">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Taux de conversion</t>
         </is>
       </c>
-      <c r="C19" s="107">
+      <c r="C19" s="69">
         <f>IFERROR(COUNTIF(K7:K13,"✅ Accepté")/COUNTA(B7:B13),0)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="B20" s="53" t="inlineStr">
+    <row r="20" ht="18.95" customHeight="1" s="74">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>CA total (acceptés)</t>
         </is>
       </c>
-      <c r="C20" s="108">
+      <c r="C20" s="70">
         <f>SUMIF(K7:K13,"✅ Accepté",I7:I13)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="B21" s="53" t="inlineStr">
+    <row r="21" ht="18.95" customHeight="1" s="74">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Montant moyen / devis</t>
         </is>
       </c>
-      <c r="C21" s="108">
+      <c r="C21" s="70">
         <f>IFERROR(AVERAGE(I7:I13),0)</f>
         <v/>
       </c>
@@ -4945,6 +4549,6 @@
     <mergeCell ref="B2:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
--- a/docs/devis/OneWay_Devis_Transport.xlsx
+++ b/docs/devis/OneWay_Devis_Transport.xlsx
@@ -10,11 +10,13 @@
     <sheet name="⚙️ Paramètres" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="🧮 Calculateur Rapide" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="📊 Historique Devis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lettres" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="🧾 Reçu de paiement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Lettres" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Vehicules">'⚙️ Paramètres'!$B$23:$B$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'📋 Devis Client'!$A$2:$J$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'🧾 Reçu de paiement'!$A$1:$J$37</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,12 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0&quot; Ar&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot; L/100&quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;+ &quot;0%"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -202,8 +205,90 @@
       <color rgb="001E3A5F"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00E07B20"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="005B6B7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="005B6B7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005B6B7F"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005B6B7F"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -255,8 +340,28 @@
         <fgColor rgb="00F4F7FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A4A72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E07B20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF0F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -366,11 +471,60 @@
         <color rgb="00D9E1EC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E1EC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E1EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E1EC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E1EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E1EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E1EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E1EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E1EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9E1EC"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,6 +872,74 @@
     <xf numFmtId="0" fontId="29" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -827,6 +1049,36 @@
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1124,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="B1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="0.5703125" customWidth="1" style="74" min="1" max="1"/>
@@ -2135,6 +2387,13 @@
         <f>"Arrêté le présent devis à la somme de "&amp;'Lettres'!$F$13&amp;" Ariary."</f>
         <v/>
       </c>
+      <c r="C53" s="121" t="n"/>
+      <c r="D53" s="121" t="n"/>
+      <c r="E53" s="121" t="n"/>
+      <c r="F53" s="121" t="n"/>
+      <c r="G53" s="121" t="n"/>
+      <c r="H53" s="121" t="n"/>
+      <c r="I53" s="122" t="n"/>
     </row>
     <row r="54" s="74">
       <c r="B54" s="92" t="n"/>
@@ -4592,10 +4851,426 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00128A4B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B3:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" style="74" min="1" max="1"/>
+    <col width="26" customWidth="1" style="74" min="2" max="2"/>
+    <col width="16" customWidth="1" style="74" min="3" max="3"/>
+    <col width="12" customWidth="1" style="74" min="4" max="4"/>
+    <col width="12" customWidth="1" style="74" min="5" max="5"/>
+    <col width="18" customWidth="1" style="74" min="6" max="6"/>
+    <col width="18" customWidth="1" style="74" min="7" max="7"/>
+    <col width="14" customWidth="1" style="74" min="8" max="8"/>
+    <col width="14" customWidth="1" style="74" min="9" max="9"/>
+    <col width="3" customWidth="1" style="74" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="18" customHeight="1" s="74"/>
+    <row r="3" ht="18" customHeight="1" s="74">
+      <c r="E3" s="123" t="inlineStr">
+        <is>
+          <t>REÇU DE PAIEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="74"/>
+    <row r="5" ht="18" customHeight="1" s="74">
+      <c r="E5" s="124" t="inlineStr">
+        <is>
+          <t>Transport · Livraison · Suivi Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="74"/>
+    <row r="7" ht="6" customHeight="1" s="74"/>
+    <row r="8" ht="20" customHeight="1" s="74">
+      <c r="B8" s="125" t="inlineStr">
+        <is>
+          <t>N° REÇU :</t>
+        </is>
+      </c>
+      <c r="C8" s="126">
+        <f>"REC-"&amp;TEXT('⚙️ Paramètres'!C9,"0000")&amp;"-"&amp;TEXT(TODAY(),"MMYYYY")</f>
+        <v/>
+      </c>
+      <c r="E8" s="125" t="inlineStr">
+        <is>
+          <t>DATE :</t>
+        </is>
+      </c>
+      <c r="F8" s="127">
+        <f>TODAY()</f>
+        <v/>
+      </c>
+      <c r="G8" s="125" t="inlineStr">
+        <is>
+          <t>RÉF. DEVIS :</t>
+        </is>
+      </c>
+      <c r="H8" s="128">
+        <f>'📋 Devis Client'!C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="6" customHeight="1" s="74"/>
+    <row r="10" ht="20" customHeight="1" s="74">
+      <c r="B10" s="129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  👤  CLIENT</t>
+        </is>
+      </c>
+      <c r="F10" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🚛  ONE WAY — TRANSPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="74">
+      <c r="B11" s="125" t="inlineStr">
+        <is>
+          <t>Nom / Société :</t>
+        </is>
+      </c>
+      <c r="C11" s="131">
+        <f>'📋 Devis Client'!C15</f>
+        <v/>
+      </c>
+      <c r="F11" s="125" t="inlineStr">
+        <is>
+          <t>Société :</t>
+        </is>
+      </c>
+      <c r="G11" s="131">
+        <f>'📋 Devis Client'!G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="74">
+      <c r="B12" s="125" t="inlineStr">
+        <is>
+          <t>Adresse :</t>
+        </is>
+      </c>
+      <c r="C12" s="131">
+        <f>'📋 Devis Client'!C16</f>
+        <v/>
+      </c>
+      <c r="F12" s="125" t="inlineStr">
+        <is>
+          <t>Adresse :</t>
+        </is>
+      </c>
+      <c r="G12" s="131">
+        <f>'📋 Devis Client'!G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="74">
+      <c r="B13" s="125" t="inlineStr">
+        <is>
+          <t>Ville :</t>
+        </is>
+      </c>
+      <c r="C13" s="131">
+        <f>'📋 Devis Client'!C17</f>
+        <v/>
+      </c>
+      <c r="F13" s="125" t="inlineStr">
+        <is>
+          <t>Téléphone :</t>
+        </is>
+      </c>
+      <c r="G13" s="131">
+        <f>'📋 Devis Client'!G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="74">
+      <c r="B14" s="125" t="inlineStr">
+        <is>
+          <t>Téléphone :</t>
+        </is>
+      </c>
+      <c r="C14" s="131">
+        <f>'📋 Devis Client'!C18</f>
+        <v/>
+      </c>
+      <c r="F14" s="125" t="inlineStr">
+        <is>
+          <t>Email :</t>
+        </is>
+      </c>
+      <c r="G14" s="131">
+        <f>'📋 Devis Client'!G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="74">
+      <c r="B15" s="125" t="inlineStr">
+        <is>
+          <t>N° Client :</t>
+        </is>
+      </c>
+      <c r="C15" s="131">
+        <f>'📋 Devis Client'!C20</f>
+        <v/>
+      </c>
+      <c r="F15" s="125" t="inlineStr">
+        <is>
+          <t>MVola :</t>
+        </is>
+      </c>
+      <c r="G15" s="131">
+        <f>'📋 Devis Client'!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="6" customHeight="1" s="74"/>
+    <row r="17" ht="22" customHeight="1" s="74">
+      <c r="B17" s="132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  💰  RÉCAPITULATIF DU RÈGLEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" s="74">
+      <c r="B18" s="133" t="inlineStr">
+        <is>
+          <t>Montant total du devis (TTC)</t>
+        </is>
+      </c>
+      <c r="G18" s="134">
+        <f>'📋 Devis Client'!G52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" s="74">
+      <c r="B19" s="135" t="inlineStr">
+        <is>
+          <t>Acompte — 50 % à la commande</t>
+        </is>
+      </c>
+      <c r="G19" s="134">
+        <f>ROUND('📋 Devis Client'!G52*0.5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" s="74">
+      <c r="B20" s="135" t="inlineStr">
+        <is>
+          <t>Solde — 50 % à la livraison</t>
+        </is>
+      </c>
+      <c r="G20" s="134">
+        <f>$G$18-$G$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="6" customHeight="1" s="74"/>
+    <row r="22" ht="22" customHeight="1" s="74">
+      <c r="B22" s="132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🧾  PAIEMENT REÇU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1" s="74">
+      <c r="B23" s="136" t="inlineStr">
+        <is>
+          <t>Nature du paiement :</t>
+        </is>
+      </c>
+      <c r="G23" s="137" t="inlineStr">
+        <is>
+          <t>Acompte 50 % (à la commande)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1" s="74">
+      <c r="B24" s="136" t="inlineStr">
+        <is>
+          <t>Mode de paiement :</t>
+        </is>
+      </c>
+      <c r="G24" s="137" t="inlineStr">
+        <is>
+          <t>MVola</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1" s="74">
+      <c r="B25" s="136" t="inlineStr">
+        <is>
+          <t>Référence transaction :</t>
+        </is>
+      </c>
+      <c r="G25" s="137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1" s="74">
+      <c r="B26" s="136" t="inlineStr">
+        <is>
+          <t>Montant libre (si nature = libre) :</t>
+        </is>
+      </c>
+      <c r="G26" s="138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1" s="74">
+      <c r="B27" s="136" t="inlineStr">
+        <is>
+          <t>Déjà encaissé (paiements précédents) :</t>
+        </is>
+      </c>
+      <c r="G27" s="138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1" s="74">
+      <c r="B28" s="139" t="inlineStr">
+        <is>
+          <t>💵  MONTANT REÇU (Ar) :</t>
+        </is>
+      </c>
+      <c r="G28" s="140">
+        <f>IF($G$23="Paiement intégral (100 %)",'📋 Devis Client'!G52,IF($G$23="Solde 50 % (à la livraison)",'📋 Devis Client'!G52-ROUND('📋 Devis Client'!G52*0.5,0),IF($G$23="Montant libre",$G$26,ROUND('📋 Devis Client'!G52*0.5,0))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" s="74">
+      <c r="B29" s="120">
+        <f>"Reçu la somme de "&amp;'Lettres'!$I$13&amp;" Ariary."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1" s="74">
+      <c r="B30" s="133" t="inlineStr">
+        <is>
+          <t>Reste à payer après ce reçu :</t>
+        </is>
+      </c>
+      <c r="G30" s="134">
+        <f>ROUND(IF($G$23="Acompte 50 % (à la commande)",'📋 Devis Client'!G52-$G$28,IF($G$23="Montant libre",MAX('📋 Devis Client'!G52-$G$27-$G$28,0),0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="74">
+      <c r="B31" s="128" t="inlineStr">
+        <is>
+          <t>Statut :</t>
+        </is>
+      </c>
+      <c r="G31" s="141">
+        <f>IF($G$30&lt;=0,"✅ SOLDÉ — Merci !","⏳ Reste à payer : "&amp;TEXT($G$30,"#,##0")&amp;" Ar")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1" s="74"/>
+    <row r="33" ht="28" customHeight="1" s="74">
+      <c r="B33" s="142" t="inlineStr">
+        <is>
+          <t>Reçu valant quittance pour le montant ci-dessus, sous réserve d'encaissement. À conserver comme justificatif de paiement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="8" customHeight="1" s="74"/>
+    <row r="35" ht="46" customHeight="1" s="74">
+      <c r="B35" s="143" t="inlineStr">
+        <is>
+          <t>Le client</t>
+        </is>
+      </c>
+      <c r="F35" s="143" t="inlineStr">
+        <is>
+          <t>Pour One Way (cachet &amp; signature)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" s="74">
+      <c r="B37" s="144" t="inlineStr">
+        <is>
+          <t>One Way SARL  ·  Transport · Livraison · Suivi Digital  ·  Antananarivo, Madagascar 🇲🇬</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="E3:I4"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="E5:I6"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B26:F26"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="G23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Acompte 50 % (à la commande),Solde 50 % (à la livraison),Paiement intégral (100 %),Montant libre"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"MVola,Orange Money,Airtel Money,Virement,Espèces"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1002"/>
+  <dimension ref="A1:I1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4613,6 +5288,15 @@
         <f>'📋 Devis Client'!$G$52</f>
         <v/>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Reçu</t>
+        </is>
+      </c>
+      <c r="I1">
+        <f>'🧾 Reçu de paiement'!$G$28</f>
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4639,13 +5323,20 @@
         <f>INT(F1)</f>
         <v/>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I2">
+        <f>INT(I1)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>g0</t>
@@ -4655,6 +5346,15 @@
         <f>MOD(F2,1000)</f>
         <v/>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>g0</t>
+        </is>
+      </c>
+      <c r="I3">
+        <f>MOD(I2,1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4679,6 +5379,15 @@
         <f>MOD(INT(F2/1000),1000)</f>
         <v/>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>g1</t>
+        </is>
+      </c>
+      <c r="I4">
+        <f>MOD(INT(I2/1000),1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4703,6 +5412,15 @@
         <f>MOD(INT(F2/1000000),1000)</f>
         <v/>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="I5">
+        <f>MOD(INT(I2/1000000),1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4727,6 +5445,15 @@
         <f>MOD(INT(F2/1000000000),1000)</f>
         <v/>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>g3</t>
+        </is>
+      </c>
+      <c r="I6">
+        <f>MOD(INT(I2/1000000000),1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4766,6 +5493,15 @@
         <f>IF(F3=0,"",INDEX($B$3:$B$1002,F3+1))</f>
         <v/>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>w0</t>
+        </is>
+      </c>
+      <c r="I8">
+        <f>IF(I3=0,"",INDEX($B$3:$B$1002,I3+1))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4790,6 +5526,15 @@
         <f>IF(F4=0,"",IF(F4=1,"mille",INDEX($C$3:$C$1002,F4+1)&amp;" mille"))</f>
         <v/>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>w1</t>
+        </is>
+      </c>
+      <c r="I9">
+        <f>IF(I4=0,"",IF(I4=1,"mille",INDEX($C$3:$C$1002,I4+1)&amp;" mille"))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4814,6 +5559,15 @@
         <f>IF(F5=0,"",INDEX($B$3:$B$1002,F5+1)&amp;IF(F5&gt;1," millions"," million"))</f>
         <v/>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>w2</t>
+        </is>
+      </c>
+      <c r="I10">
+        <f>IF(I5=0,"",INDEX($B$3:$B$1002,I5+1)&amp;IF(I5&gt;1," millions"," million"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4838,6 +5592,15 @@
         <f>IF(F6=0,"",INDEX($B$3:$B$1002,F6+1)&amp;IF(F6&gt;1," milliards"," milliard"))</f>
         <v/>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>w3</t>
+        </is>
+      </c>
+      <c r="I11">
+        <f>IF(I6=0,"",INDEX($B$3:$B$1002,I6+1)&amp;IF(I6&gt;1," milliards"," milliard"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4875,6 +5638,15 @@
       </c>
       <c r="F13">
         <f>IF(F2=0,"zéro",TRIM(F11&amp;" "&amp;F10&amp;" "&amp;F9&amp;" "&amp;F8))</f>
+        <v/>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>lettres</t>
+        </is>
+      </c>
+      <c r="I13">
+        <f>IF(I2=0,"zéro",TRIM(I11&amp;" "&amp;I10&amp;" "&amp;I9&amp;" "&amp;I8))</f>
         <v/>
       </c>
     </row>

--- a/docs/devis/OneWay_Devis_Transport.xlsx
+++ b/docs/devis/OneWay_Devis_Transport.xlsx
@@ -16,6 +16,7 @@
   <definedNames>
     <definedName name="Vehicules">'⚙️ Paramètres'!$B$23:$B$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'📋 Devis Client'!$A$2:$J$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'📊 Historique Devis'!$A$1:$R$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'🧾 Reçu de paiement'!$A$1:$J$37</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -524,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -940,6 +941,7 @@
     <xf numFmtId="0" fontId="43" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1079,6 +1081,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4304,7 +4309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L21"/>
+  <dimension ref="B2:Q26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="74" min="1" max="1"/>
@@ -4317,7 +4322,12 @@
     <col width="14" customWidth="1" style="74" min="9" max="10"/>
     <col width="13" customWidth="1" style="74" min="11" max="11"/>
     <col width="18" customWidth="1" style="74" min="12" max="12"/>
-    <col width="3" customWidth="1" style="74" min="13" max="13"/>
+    <col width="14" customWidth="1" style="74" min="13" max="13"/>
+    <col width="14" customWidth="1" style="74" min="14" max="14"/>
+    <col width="14" customWidth="1" style="74" min="15" max="15"/>
+    <col width="14" customWidth="1" style="74" min="16" max="16"/>
+    <col width="13" customWidth="1" style="74" min="17" max="17"/>
+    <col width="3" customWidth="1" style="74" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -4386,6 +4396,31 @@
           <t>NOTES</t>
         </is>
       </c>
+      <c r="M6" s="103" t="inlineStr">
+        <is>
+          <t>ACOMPTE (Ar)</t>
+        </is>
+      </c>
+      <c r="N6" s="103" t="inlineStr">
+        <is>
+          <t>SOLDE (Ar)</t>
+        </is>
+      </c>
+      <c r="O6" s="103" t="inlineStr">
+        <is>
+          <t>ENCAISSÉ (Ar)</t>
+        </is>
+      </c>
+      <c r="P6" s="103" t="inlineStr">
+        <is>
+          <t>RESTE (Ar)</t>
+        </is>
+      </c>
+      <c r="Q6" s="103" t="inlineStr">
+        <is>
+          <t>PAIEMENT</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18.95" customHeight="1" s="74">
       <c r="B7" s="51" t="inlineStr">
@@ -4439,6 +4474,24 @@
           <t>Livraison OK</t>
         </is>
       </c>
+      <c r="M7" s="12" t="n">
+        <v>1441500</v>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>1441500</v>
+      </c>
+      <c r="O7" s="12">
+        <f>IF(K7&lt;&gt;"✅ Accepté","",N7+M7)</f>
+        <v/>
+      </c>
+      <c r="P7" s="12">
+        <f>IF(K7&lt;&gt;"✅ Accepté","",J7-M7-N7)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="62">
+        <f>IF(K7&lt;&gt;"✅ Accepté","—",IF(M7+N7&gt;=J7,"✅ Soldé",IF(M7+N7&lt;=0,"❌ Impayé","⏳ Partiel")))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="18.95" customHeight="1" s="74">
       <c r="B8" s="53" t="inlineStr">
@@ -4492,6 +4545,24 @@
           <t>Marchandises générales</t>
         </is>
       </c>
+      <c r="M8" s="24" t="n">
+        <v>465500</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>465500</v>
+      </c>
+      <c r="O8" s="24">
+        <f>IF(K8&lt;&gt;"✅ Accepté","",N8+M8)</f>
+        <v/>
+      </c>
+      <c r="P8" s="24">
+        <f>IF(K8&lt;&gt;"✅ Accepté","",J8-M8-N8)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="65">
+        <f>IF(K8&lt;&gt;"✅ Accepté","—",IF(M8+N8&gt;=J8,"✅ Soldé",IF(M8+N8&lt;=0,"❌ Impayé","⏳ Partiel")))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="18.95" customHeight="1" s="74">
       <c r="B9" s="51" t="inlineStr">
@@ -4545,6 +4616,22 @@
           <t>Périssables urgents</t>
         </is>
       </c>
+      <c r="M9" s="12" t="n">
+        <v>1889500</v>
+      </c>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12">
+        <f>IF(K9&lt;&gt;"✅ Accepté","",N9+M9)</f>
+        <v/>
+      </c>
+      <c r="P9" s="12">
+        <f>IF(K9&lt;&gt;"✅ Accepté","",J9-M9-N9)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="62">
+        <f>IF(K9&lt;&gt;"✅ Accepté","—",IF(M9+N9&gt;=J9,"✅ Soldé",IF(M9+N9&lt;=0,"❌ Impayé","⏳ Partiel")))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="18.95" customHeight="1" s="74">
       <c r="B10" s="53" t="inlineStr">
@@ -4598,6 +4685,22 @@
           <t>Semi-remorque</t>
         </is>
       </c>
+      <c r="M10" s="24" t="n">
+        <v>3289500</v>
+      </c>
+      <c r="N10" s="24" t="n"/>
+      <c r="O10" s="24">
+        <f>IF(K10&lt;&gt;"✅ Accepté","",N10+M10)</f>
+        <v/>
+      </c>
+      <c r="P10" s="24">
+        <f>IF(K10&lt;&gt;"✅ Accepté","",J10-M10-N10)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="65">
+        <f>IF(K10&lt;&gt;"✅ Accepté","—",IF(M10+N10&gt;=J10,"✅ Soldé",IF(M10+N10&lt;=0,"❌ Impayé","⏳ Partiel")))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="18.95" customHeight="1" s="74">
       <c r="B11" s="51" t="inlineStr">
@@ -4651,6 +4754,20 @@
           <t>En cours</t>
         </is>
       </c>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12">
+        <f>IF(K11&lt;&gt;"✅ Accepté","",N11+M11)</f>
+        <v/>
+      </c>
+      <c r="P11" s="12">
+        <f>IF(K11&lt;&gt;"✅ Accepté","",J11-M11-N11)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="62">
+        <f>IF(K11&lt;&gt;"✅ Accepté","—",IF(M11+N11&gt;=J11,"✅ Soldé",IF(M11+N11&lt;=0,"❌ Impayé","⏳ Partiel")))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="18.95" customHeight="1" s="74">
       <c r="B12" s="53" t="inlineStr">
@@ -4704,6 +4821,20 @@
           <t>Prix refusé</t>
         </is>
       </c>
+      <c r="M12" s="24" t="n"/>
+      <c r="N12" s="24" t="n"/>
+      <c r="O12" s="24">
+        <f>IF(K12&lt;&gt;"✅ Accepté","",N12+M12)</f>
+        <v/>
+      </c>
+      <c r="P12" s="24">
+        <f>IF(K12&lt;&gt;"✅ Accepté","",J12-M12-N12)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="65">
+        <f>IF(K12&lt;&gt;"✅ Accepté","—",IF(M12+N12&gt;=J12,"✅ Soldé",IF(M12+N12&lt;=0,"❌ Impayé","⏳ Partiel")))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="18.95" customHeight="1" s="74">
       <c r="B13" s="51" t="inlineStr">
@@ -4756,6 +4887,20 @@
         <is>
           <t>Devis émis</t>
         </is>
+      </c>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12">
+        <f>IF(K13&lt;&gt;"✅ Accepté","",N13+M13)</f>
+        <v/>
+      </c>
+      <c r="P13" s="12">
+        <f>IF(K13&lt;&gt;"✅ Accepté","",J13-M13-N13)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="62">
+        <f>IF(K13&lt;&gt;"✅ Accepté","—",IF(M13+N13&gt;=J13,"✅ Soldé",IF(M13+N13&lt;=0,"❌ Impayé","⏳ Partiel")))</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="21.95" customHeight="1" s="74">
@@ -4774,6 +4919,23 @@
       </c>
       <c r="K14" s="28" t="n"/>
       <c r="L14" s="28" t="n"/>
+      <c r="M14" s="67">
+        <f>SUMIF($K$7:$K$13,"✅ Accepté",M7:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="67">
+        <f>SUMIF($K$7:$K$13,"✅ Accepté",N7:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="67">
+        <f>SUMIF($K$7:$K$13,"✅ Accepté",O7:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="67">
+        <f>SUMIF($K$7:$K$13,"✅ Accepté",P7:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="67" t="n"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" s="74">
       <c r="B16" s="113" t="inlineStr">
@@ -4837,11 +4999,66 @@
         <v/>
       </c>
     </row>
+    <row r="22" ht="18.9" customHeight="1" s="74">
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Total facturé (acceptés)</t>
+        </is>
+      </c>
+      <c r="C22" s="70">
+        <f>SUMIF($K$7:$K$13,"✅ Accepté",J7:J13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18.9" customHeight="1" s="74">
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Total encaissé</t>
+        </is>
+      </c>
+      <c r="C23" s="70">
+        <f>SUM(O7:O13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18.9" customHeight="1" s="74">
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>Reste à encaisser</t>
+        </is>
+      </c>
+      <c r="C24" s="70">
+        <f>SUMIF($K$7:$K$13,"✅ Accepté",P7:P13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18.9" customHeight="1" s="74">
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Taux d'encaissement</t>
+        </is>
+      </c>
+      <c r="C25" s="69">
+        <f>IFERROR(C23/C22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18.9" customHeight="1" s="74">
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>Devis soldés / partiels</t>
+        </is>
+      </c>
+      <c r="C26" s="108">
+        <f>COUNTIF(Q7:Q13,"✅ Soldé")&amp;" / "&amp;COUNTIF(Q7:Q13,"⏳ Partiel")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B16:L16"/>
+    <mergeCell ref="B16:Q16"/>
     <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B2:L4"/>
+    <mergeCell ref="B2:Q4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
@@ -5090,6 +5307,8 @@
           <t>Acompte 50 % (à la commande)</t>
         </is>
       </c>
+      <c r="H23" s="121" t="n"/>
+      <c r="I23" s="122" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1" s="74">
       <c r="B24" s="136" t="inlineStr">
@@ -5102,6 +5321,8 @@
           <t>MVola</t>
         </is>
       </c>
+      <c r="H24" s="121" t="n"/>
+      <c r="I24" s="122" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1" s="74">
       <c r="B25" s="136" t="inlineStr">
@@ -5114,6 +5335,8 @@
           <t>—</t>
         </is>
       </c>
+      <c r="H25" s="121" t="n"/>
+      <c r="I25" s="122" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1" s="74">
       <c r="B26" s="136" t="inlineStr">
@@ -5124,6 +5347,8 @@
       <c r="G26" s="138" t="n">
         <v>0</v>
       </c>
+      <c r="H26" s="121" t="n"/>
+      <c r="I26" s="122" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1" s="74">
       <c r="B27" s="136" t="inlineStr">
@@ -5134,6 +5359,8 @@
       <c r="G27" s="138" t="n">
         <v>0</v>
       </c>
+      <c r="H27" s="121" t="n"/>
+      <c r="I27" s="122" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1" s="74">
       <c r="B28" s="139" t="inlineStr">
@@ -5151,6 +5378,13 @@
         <f>"Reçu la somme de "&amp;'Lettres'!$I$13&amp;" Ariary."</f>
         <v/>
       </c>
+      <c r="C29" s="121" t="n"/>
+      <c r="D29" s="121" t="n"/>
+      <c r="E29" s="121" t="n"/>
+      <c r="F29" s="121" t="n"/>
+      <c r="G29" s="121" t="n"/>
+      <c r="H29" s="121" t="n"/>
+      <c r="I29" s="122" t="n"/>
     </row>
     <row r="30" ht="19" customHeight="1" s="74">
       <c r="B30" s="133" t="inlineStr">
@@ -5189,11 +5423,17 @@
           <t>Le client</t>
         </is>
       </c>
+      <c r="C35" s="145" t="n"/>
+      <c r="D35" s="145" t="n"/>
+      <c r="E35" s="145" t="n"/>
       <c r="F35" s="143" t="inlineStr">
         <is>
           <t>Pour One Way (cachet &amp; signature)</t>
         </is>
       </c>
+      <c r="G35" s="145" t="n"/>
+      <c r="H35" s="145" t="n"/>
+      <c r="I35" s="145" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1" s="74">
       <c r="B37" s="144" t="inlineStr">
@@ -5214,8 +5454,8 @@
     <mergeCell ref="G30:I30"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="B27:F27"/>
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="G14:I14"/>
